--- a/Impacts_and_Hazards_List.xlsx
+++ b/Impacts_and_Hazards_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GnegyE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02EFCDA8-AA75-4705-ABA4-8C453C2F2FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55CBA0B-ECCA-43D9-B173-6CA93CCC142C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1200" windowWidth="27765" windowHeight="13935" firstSheet="1" activeTab="1" xr2:uid="{E3F7029F-E709-498F-9C5C-01D4BE67A35F}"/>
+    <workbookView xWindow="735" yWindow="840" windowWidth="27765" windowHeight="13935" firstSheet="1" activeTab="1" xr2:uid="{E3F7029F-E709-498F-9C5C-01D4BE67A35F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hazard Proxies (unclean)" sheetId="7" state="hidden" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5537" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5538" uniqueCount="1186">
   <si>
     <t>Hazard Leopard Team Member Leading</t>
   </si>
@@ -3120,9 +3120,6 @@
     <t>Relevant Literature and Resources</t>
   </si>
   <si>
-    <t xml:space="preserve">Impact Statement for Buildings: </t>
-  </si>
-  <si>
     <t>Phase 1.1</t>
   </si>
   <si>
@@ -8047,6 +8044,9 @@
   </si>
   <si>
     <t>IPCC WG1 Interactive Atlas</t>
+  </si>
+  <si>
+    <t>Impact Statement for Buildings</t>
   </si>
 </sst>
 </file>
@@ -8641,7 +8641,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9078,6 +9078,9 @@
     <xf numFmtId="0" fontId="47" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10448,10 +10451,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3B39AE6F-E3D6-4F7D-86CF-A61884E85639}" name="HazardProxies" displayName="HazardProxies" ref="A1:AC125" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <autoFilter ref="A1:AC125" xr:uid="{A4D2F648-11ED-408B-910F-54E516A1E7ED}">
@@ -10553,7 +10552,7 @@
     <tableColumn id="26" xr3:uid="{06E22BBD-59ED-47CF-A5EB-E00EE35C5D36}" name="End-User Type_x000a_General Public_x000a_Somewhat Experienced_x000a_SME/Research" dataDxfId="3"/>
     <tableColumn id="27" xr3:uid="{0ADF2C28-21F2-421C-88FE-8F21BA18ECD4}" name="General Comments" dataDxfId="2"/>
     <tableColumn id="28" xr3:uid="{0691E6A6-6697-4281-BBE3-74D1D01176D2}" name="Expert Reviewer" dataDxfId="1"/>
-    <tableColumn id="32" xr3:uid="{4FD72034-A642-4E2B-8A66-60EE62E029E8}" name="Impact Statement for Buildings: " dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{4FD72034-A642-4E2B-8A66-60EE62E029E8}" name="Impact Statement for Buildings" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -19473,7 +19472,7 @@
     <col min="35" max="35" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="93" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="93" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
@@ -19570,8 +19569,11 @@
       <c r="AH1" s="93" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" s="64" customFormat="1" ht="360" x14ac:dyDescent="0.25">
+      <c r="AI1" s="154" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" s="64" customFormat="1" ht="360.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="60" t="s">
         <v>0</v>
       </c>
@@ -19675,7 +19677,7 @@
         <v>28</v>
       </c>
       <c r="AI2" s="8" t="s">
-        <v>572</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -19683,25 +19685,25 @@
         <v>29</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C3" s="45" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="100" t="s">
+        <v>573</v>
+      </c>
+      <c r="E3" s="127" t="s">
         <v>574</v>
       </c>
-      <c r="E3" s="127" t="s">
+      <c r="F3" s="127" t="s">
         <v>575</v>
-      </c>
-      <c r="F3" s="127" t="s">
-        <v>576</v>
       </c>
       <c r="G3" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I3" s="43" t="s">
         <v>36</v>
@@ -19719,14 +19721,14 @@
         <v>375</v>
       </c>
       <c r="N3" s="129" t="s">
+        <v>577</v>
+      </c>
+      <c r="O3" s="129" t="s">
         <v>578</v>
-      </c>
-      <c r="O3" s="129" t="s">
-        <v>579</v>
       </c>
       <c r="P3" s="43"/>
       <c r="Q3" s="43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R3" s="43" t="s">
         <v>43</v>
@@ -19747,16 +19749,16 @@
         <v>201</v>
       </c>
       <c r="X3" s="148" t="s">
+        <v>580</v>
+      </c>
+      <c r="Y3" s="151" t="s">
         <v>581</v>
-      </c>
-      <c r="Y3" s="151" t="s">
-        <v>582</v>
       </c>
       <c r="Z3" s="43"/>
       <c r="AA3" s="43"/>
       <c r="AB3" s="43"/>
       <c r="AC3" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AD3" s="43" t="s">
         <v>201</v>
@@ -19768,29 +19770,29 @@
         <v>51</v>
       </c>
       <c r="AI3" s="129" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="273.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45"/>
       <c r="B4" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C4" s="45"/>
       <c r="D4" s="100" t="s">
+        <v>573</v>
+      </c>
+      <c r="E4" s="127" t="s">
         <v>574</v>
       </c>
-      <c r="E4" s="127" t="s">
+      <c r="F4" s="127" t="s">
         <v>575</v>
-      </c>
-      <c r="F4" s="127" t="s">
-        <v>576</v>
       </c>
       <c r="G4" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I4" s="43" t="s">
         <v>36</v>
@@ -19806,10 +19808,10 @@
         <v>283</v>
       </c>
       <c r="N4" s="129" t="s">
+        <v>584</v>
+      </c>
+      <c r="O4" s="129" t="s">
         <v>585</v>
-      </c>
-      <c r="O4" s="129" t="s">
-        <v>586</v>
       </c>
       <c r="P4" s="43"/>
       <c r="Q4" s="43"/>
@@ -19820,16 +19822,16 @@
       <c r="V4" s="43"/>
       <c r="W4" s="43"/>
       <c r="X4" s="148" t="s">
+        <v>586</v>
+      </c>
+      <c r="Y4" s="151" t="s">
         <v>587</v>
-      </c>
-      <c r="Y4" s="151" t="s">
-        <v>588</v>
       </c>
       <c r="Z4" s="43"/>
       <c r="AA4" s="43"/>
       <c r="AB4" s="43"/>
       <c r="AC4" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AD4" s="43"/>
       <c r="AE4" s="43"/>
@@ -19837,29 +19839,29 @@
       <c r="AG4" s="6"/>
       <c r="AH4" s="43"/>
       <c r="AI4" s="129" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="225" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="45"/>
       <c r="B5" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="100" t="s">
+        <v>573</v>
+      </c>
+      <c r="E5" s="127" t="s">
         <v>574</v>
       </c>
-      <c r="E5" s="127" t="s">
+      <c r="F5" s="127" t="s">
         <v>575</v>
-      </c>
-      <c r="F5" s="127" t="s">
-        <v>576</v>
       </c>
       <c r="G5" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I5" s="43" t="s">
         <v>36</v>
@@ -19875,10 +19877,10 @@
         <v>109</v>
       </c>
       <c r="N5" s="129" t="s">
+        <v>590</v>
+      </c>
+      <c r="O5" s="129" t="s">
         <v>591</v>
-      </c>
-      <c r="O5" s="129" t="s">
-        <v>592</v>
       </c>
       <c r="P5" s="43"/>
       <c r="Q5" s="43"/>
@@ -19889,7 +19891,7 @@
       <c r="V5" s="43"/>
       <c r="W5" s="43"/>
       <c r="X5" s="148" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Y5" s="151" t="s">
         <v>86</v>
@@ -19898,7 +19900,7 @@
       <c r="AA5" s="43"/>
       <c r="AB5" s="43"/>
       <c r="AC5" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AD5" s="43"/>
       <c r="AE5" s="43"/>
@@ -19906,7 +19908,7 @@
       <c r="AG5" s="6"/>
       <c r="AH5" s="43"/>
       <c r="AI5" s="129" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -19923,16 +19925,16 @@
         <v>54</v>
       </c>
       <c r="E6" s="46" t="s">
+        <v>595</v>
+      </c>
+      <c r="F6" s="46" t="s">
         <v>596</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>597</v>
       </c>
       <c r="G6" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I6" s="43" t="s">
         <v>57</v>
@@ -19941,23 +19943,23 @@
         <v>37</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L6" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="76" t="s">
+        <v>599</v>
+      </c>
+      <c r="N6" s="43" t="s">
         <v>600</v>
-      </c>
-      <c r="N6" s="43" t="s">
-        <v>601</v>
       </c>
       <c r="O6" s="43"/>
       <c r="P6" s="43" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q6" s="48" t="s">
         <v>602</v>
-      </c>
-      <c r="Q6" s="48" t="s">
-        <v>603</v>
       </c>
       <c r="R6" s="43" t="s">
         <v>62</v>
@@ -19981,7 +19983,7 @@
         <v>86</v>
       </c>
       <c r="Y6" s="144" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Z6" s="43" t="s">
         <v>49</v>
@@ -19991,18 +19993,18 @@
         <v>118</v>
       </c>
       <c r="AC6" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD6" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD6" s="23" t="s">
+      <c r="AE6" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF6" s="6"/>
       <c r="AG6" s="23"/>
       <c r="AH6" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI6" s="1"/>
     </row>
@@ -20018,16 +20020,16 @@
         <v>54</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G7" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I7" s="43" t="s">
         <v>57</v>
@@ -20036,23 +20038,23 @@
         <v>37</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L7" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M7" s="76" t="s">
+        <v>610</v>
+      </c>
+      <c r="N7" s="23" t="s">
         <v>611</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>612</v>
       </c>
       <c r="O7" s="90"/>
       <c r="P7" s="90" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Q7" s="48" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R7" s="43"/>
       <c r="S7" s="43" t="s">
@@ -20063,35 +20065,35 @@
       </c>
       <c r="U7" s="23"/>
       <c r="V7" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="W7" s="90" t="s">
         <v>614</v>
-      </c>
-      <c r="W7" s="90" t="s">
-        <v>615</v>
       </c>
       <c r="X7" s="119" t="s">
         <v>37</v>
       </c>
       <c r="Y7" s="119"/>
       <c r="Z7" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="AA7" s="23" t="s">
         <v>616</v>
-      </c>
-      <c r="AA7" s="23" t="s">
-        <v>617</v>
       </c>
       <c r="AB7" s="23"/>
       <c r="AC7" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD7" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD7" s="23" t="s">
+      <c r="AE7" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF7" s="6"/>
       <c r="AG7" s="23"/>
       <c r="AH7" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI7" s="1"/>
     </row>
@@ -20107,16 +20109,16 @@
         <v>54</v>
       </c>
       <c r="E8" s="67" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F8" s="67" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G8" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I8" s="43" t="s">
         <v>57</v>
@@ -20125,21 +20127,21 @@
         <v>37</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L8" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M8" s="76" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="N8" s="23"/>
       <c r="O8" s="90"/>
       <c r="P8" s="90" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="Q8" s="48" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R8" s="43"/>
       <c r="S8" s="43" t="s">
@@ -20150,35 +20152,35 @@
       </c>
       <c r="U8" s="23"/>
       <c r="V8" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="W8" s="90" t="s">
         <v>614</v>
-      </c>
-      <c r="W8" s="90" t="s">
-        <v>615</v>
       </c>
       <c r="X8" s="119" t="s">
         <v>37</v>
       </c>
       <c r="Y8" s="119"/>
       <c r="Z8" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="AA8" s="23" t="s">
         <v>616</v>
-      </c>
-      <c r="AA8" s="23" t="s">
-        <v>617</v>
       </c>
       <c r="AB8" s="23"/>
       <c r="AC8" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD8" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD8" s="23" t="s">
+      <c r="AE8" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF8" s="6"/>
       <c r="AG8" s="23"/>
       <c r="AH8" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI8" s="1"/>
     </row>
@@ -20196,10 +20198,10 @@
         <v>69</v>
       </c>
       <c r="E9" s="43" t="s">
+        <v>619</v>
+      </c>
+      <c r="F9" s="43" t="s">
         <v>620</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>621</v>
       </c>
       <c r="G9" s="46" t="s">
         <v>55</v>
@@ -20212,23 +20214,23 @@
         <v>37</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L9" s="43" t="s">
         <v>125</v>
       </c>
       <c r="M9" s="76" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O9" s="43"/>
       <c r="P9" s="43" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q9" s="43" t="s">
         <v>602</v>
-      </c>
-      <c r="Q9" s="43" t="s">
-        <v>603</v>
       </c>
       <c r="R9" s="43" t="s">
         <v>75</v>
@@ -20260,7 +20262,7 @@
         <v>118</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD9" s="23" t="s">
         <v>67</v>
@@ -20268,10 +20270,10 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="6"/>
       <c r="AG9" s="23" t="s">
+        <v>622</v>
+      </c>
+      <c r="AH9" s="43" t="s">
         <v>623</v>
-      </c>
-      <c r="AH9" s="43" t="s">
-        <v>624</v>
       </c>
       <c r="AI9" s="1"/>
     </row>
@@ -20289,10 +20291,10 @@
         <v>69</v>
       </c>
       <c r="E10" s="43" t="s">
+        <v>619</v>
+      </c>
+      <c r="F10" s="43" t="s">
         <v>620</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>621</v>
       </c>
       <c r="G10" s="46" t="s">
         <v>55</v>
@@ -20311,17 +20313,17 @@
         <v>125</v>
       </c>
       <c r="M10" s="76" t="s">
+        <v>624</v>
+      </c>
+      <c r="N10" s="43" t="s">
         <v>625</v>
-      </c>
-      <c r="N10" s="43" t="s">
-        <v>626</v>
       </c>
       <c r="O10" s="48"/>
       <c r="P10" s="90" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q10" s="90" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R10" s="43" t="s">
         <v>75</v>
@@ -20351,14 +20353,14 @@
         <v>118</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD10" s="23"/>
       <c r="AE10" s="23"/>
       <c r="AF10" s="6"/>
       <c r="AG10" s="23"/>
       <c r="AH10" s="23" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AI10" s="1"/>
     </row>
@@ -20376,16 +20378,16 @@
         <v>81</v>
       </c>
       <c r="E11" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F11" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>629</v>
       </c>
       <c r="G11" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I11" s="43" t="s">
         <v>82</v>
@@ -20403,14 +20405,14 @@
         <v>83</v>
       </c>
       <c r="N11" s="43" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="O11" s="43"/>
       <c r="P11" s="43" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Q11" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R11" s="43" t="s">
         <v>75</v>
@@ -20440,18 +20442,18 @@
         <v>118</v>
       </c>
       <c r="AC11" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD11" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD11" s="23" t="s">
+      <c r="AE11" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE11" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF11" s="6"/>
       <c r="AG11" s="23"/>
       <c r="AH11" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI11" s="1"/>
     </row>
@@ -20469,16 +20471,16 @@
         <v>81</v>
       </c>
       <c r="E12" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F12" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>629</v>
       </c>
       <c r="G12" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I12" s="43" t="s">
         <v>82</v>
@@ -20493,17 +20495,17 @@
         <v>125</v>
       </c>
       <c r="M12" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="N12" s="108" t="s">
         <v>631</v>
-      </c>
-      <c r="N12" s="108" t="s">
-        <v>632</v>
       </c>
       <c r="O12" s="108"/>
       <c r="P12" s="43" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R12" s="43" t="s">
         <v>75</v>
@@ -20533,18 +20535,18 @@
         <v>118</v>
       </c>
       <c r="AC12" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD12" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD12" s="23" t="s">
+      <c r="AE12" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF12" s="6"/>
       <c r="AG12" s="23"/>
       <c r="AH12" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI12" s="1"/>
     </row>
@@ -20562,16 +20564,16 @@
         <v>81</v>
       </c>
       <c r="E13" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F13" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>629</v>
       </c>
       <c r="G13" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I13" s="43" t="s">
         <v>82</v>
@@ -20580,7 +20582,7 @@
         <v>37</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L13" s="43" t="s">
         <v>125</v>
@@ -20593,10 +20595,10 @@
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="43" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="Q13" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R13" s="43" t="s">
         <v>75</v>
@@ -20624,20 +20626,20 @@
         <v>118</v>
       </c>
       <c r="AC13" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD13" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD13" s="23" t="s">
+      <c r="AE13" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE13" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF13" s="6"/>
       <c r="AG13" s="23" t="s">
         <v>80</v>
       </c>
       <c r="AH13" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI13" s="1"/>
     </row>
@@ -20653,16 +20655,16 @@
         <v>81</v>
       </c>
       <c r="E14" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F14" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>629</v>
       </c>
       <c r="G14" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I14" s="43" t="s">
         <v>82</v>
@@ -20671,21 +20673,21 @@
         <v>71</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L14" s="43" t="s">
         <v>125</v>
       </c>
       <c r="M14" s="76" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="N14" s="23"/>
       <c r="O14" s="90"/>
       <c r="P14" s="90" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q14" s="48" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R14" s="43"/>
       <c r="S14" s="43" t="s">
@@ -20696,35 +20698,35 @@
       </c>
       <c r="U14" s="23"/>
       <c r="V14" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="W14" s="90" t="s">
         <v>614</v>
-      </c>
-      <c r="W14" s="90" t="s">
-        <v>615</v>
       </c>
       <c r="X14" s="119" t="s">
         <v>37</v>
       </c>
       <c r="Y14" s="119"/>
       <c r="Z14" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="AA14" s="23" t="s">
         <v>616</v>
-      </c>
-      <c r="AA14" s="23" t="s">
-        <v>617</v>
       </c>
       <c r="AB14" s="23"/>
       <c r="AC14" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD14" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="AD14" s="23" t="s">
+      <c r="AE14" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="AF14" s="6"/>
       <c r="AG14" s="23"/>
       <c r="AH14" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI14" s="1"/>
     </row>
@@ -20740,16 +20742,16 @@
         <v>81</v>
       </c>
       <c r="E15" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F15" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>629</v>
       </c>
       <c r="G15" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I15" s="43" t="s">
         <v>82</v>
@@ -20758,18 +20760,18 @@
         <v>71</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L15" s="43" t="s">
         <v>125</v>
       </c>
       <c r="M15" s="76" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="N15" s="23"/>
       <c r="O15" s="90"/>
       <c r="P15" s="90" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="Q15" s="43"/>
       <c r="R15" s="43"/>
@@ -20786,12 +20788,12 @@
       <c r="AC15" s="23"/>
       <c r="AD15" s="23"/>
       <c r="AE15" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AF15" s="6"/>
       <c r="AG15" s="23"/>
       <c r="AH15" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI15" s="1"/>
     </row>
@@ -20809,16 +20811,16 @@
         <v>87</v>
       </c>
       <c r="E16" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F16" s="43" t="s">
         <v>638</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>639</v>
       </c>
       <c r="G16" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I16" s="43" t="s">
         <v>37</v>
@@ -20827,7 +20829,7 @@
         <v>88</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>125</v>
@@ -20840,10 +20842,10 @@
       </c>
       <c r="O16" s="43"/>
       <c r="P16" s="43" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q16" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R16" s="43" t="s">
         <v>62</v>
@@ -20871,20 +20873,20 @@
         <v>118</v>
       </c>
       <c r="AC16" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD16" s="23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AF16" s="6"/>
       <c r="AG16" s="23" t="s">
         <v>80</v>
       </c>
       <c r="AH16" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI16" s="1"/>
     </row>
@@ -20900,16 +20902,16 @@
         <v>87</v>
       </c>
       <c r="E17" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F17" s="43" t="s">
         <v>638</v>
-      </c>
-      <c r="F17" s="43" t="s">
-        <v>639</v>
       </c>
       <c r="G17" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I17" s="43" t="s">
         <v>37</v>
@@ -20918,23 +20920,23 @@
         <v>88</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L17" s="43" t="s">
         <v>125</v>
       </c>
       <c r="M17" s="76" t="s">
+        <v>641</v>
+      </c>
+      <c r="N17" s="6" t="s">
         <v>642</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>643</v>
       </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="Q17" s="43" t="s">
         <v>644</v>
-      </c>
-      <c r="Q17" s="43" t="s">
-        <v>645</v>
       </c>
       <c r="R17" s="43"/>
       <c r="S17" s="43" t="s">
@@ -20945,34 +20947,34 @@
       </c>
       <c r="U17" s="23"/>
       <c r="V17" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="W17" s="90" t="s">
         <v>614</v>
-      </c>
-      <c r="W17" s="90" t="s">
-        <v>615</v>
       </c>
       <c r="X17" s="119" t="s">
         <v>37</v>
       </c>
       <c r="Y17" s="119"/>
       <c r="Z17" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="AA17" s="23" t="s">
         <v>616</v>
-      </c>
-      <c r="AA17" s="23" t="s">
-        <v>617</v>
       </c>
       <c r="AB17" s="23"/>
       <c r="AC17" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD17" s="23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AF17" s="23"/>
       <c r="AG17" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AH17" s="6"/>
       <c r="AI17" s="1"/>
@@ -20991,16 +20993,16 @@
         <v>87</v>
       </c>
       <c r="E18" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F18" s="43" t="s">
         <v>638</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>639</v>
       </c>
       <c r="G18" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I18" s="43" t="s">
         <v>37</v>
@@ -21025,7 +21027,7 @@
         <v>90</v>
       </c>
       <c r="Q18" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R18" s="43" t="s">
         <v>75</v>
@@ -21051,18 +21053,18 @@
         <v>118</v>
       </c>
       <c r="AC18" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD18" s="23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AF18" s="6"/>
       <c r="AG18" s="23"/>
       <c r="AH18" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI18" s="1"/>
     </row>
@@ -21080,10 +21082,10 @@
         <v>87</v>
       </c>
       <c r="E19" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F19" s="43" t="s">
         <v>638</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>639</v>
       </c>
       <c r="G19" s="46" t="s">
         <v>34</v>
@@ -21102,7 +21104,7 @@
         <v>125</v>
       </c>
       <c r="M19" s="76" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N19" s="43" t="s">
         <v>60</v>
@@ -21112,7 +21114,7 @@
         <v>90</v>
       </c>
       <c r="Q19" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R19" s="43" t="s">
         <v>62</v>
@@ -21138,18 +21140,18 @@
         <v>118</v>
       </c>
       <c r="AC19" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD19" s="23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AF19" s="6"/>
       <c r="AG19" s="23"/>
       <c r="AH19" s="43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AI19" s="1"/>
     </row>
@@ -21167,16 +21169,16 @@
         <v>99</v>
       </c>
       <c r="E20" s="127" t="s">
+        <v>646</v>
+      </c>
+      <c r="F20" s="127" t="s">
         <v>647</v>
-      </c>
-      <c r="F20" s="127" t="s">
-        <v>648</v>
       </c>
       <c r="G20" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I20" s="43" t="s">
         <v>101</v>
@@ -21194,14 +21196,14 @@
         <v>103</v>
       </c>
       <c r="N20" s="129" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="O20" s="129"/>
       <c r="P20" s="43" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q20" s="43" t="s">
         <v>650</v>
-      </c>
-      <c r="Q20" s="43" t="s">
-        <v>651</v>
       </c>
       <c r="R20" s="43" t="s">
         <v>62</v>
@@ -21220,10 +21222,10 @@
       </c>
       <c r="W20" s="23"/>
       <c r="X20" s="149" t="s">
+        <v>651</v>
+      </c>
+      <c r="Y20" s="151" t="s">
         <v>652</v>
-      </c>
-      <c r="Y20" s="151" t="s">
-        <v>653</v>
       </c>
       <c r="Z20" s="43" t="s">
         <v>49</v>
@@ -21233,19 +21235,19 @@
         <v>118</v>
       </c>
       <c r="AC20" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="AD20" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="AD20" s="23" t="s">
+      <c r="AE20" s="23" t="s">
         <v>655</v>
-      </c>
-      <c r="AE20" s="23" t="s">
-        <v>656</v>
       </c>
       <c r="AF20" s="6"/>
       <c r="AG20" s="23"/>
       <c r="AH20" s="43"/>
       <c r="AI20" s="134" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="21" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -21262,16 +21264,16 @@
         <v>99</v>
       </c>
       <c r="E21" s="127" t="s">
+        <v>646</v>
+      </c>
+      <c r="F21" s="127" t="s">
         <v>647</v>
-      </c>
-      <c r="F21" s="127" t="s">
-        <v>648</v>
       </c>
       <c r="G21" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I21" s="43" t="s">
         <v>101</v>
@@ -21289,14 +21291,14 @@
         <v>109</v>
       </c>
       <c r="N21" s="129" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="O21" s="129"/>
       <c r="P21" s="46" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q21" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R21" s="43" t="s">
         <v>75</v>
@@ -21315,7 +21317,7 @@
       </c>
       <c r="W21" s="23"/>
       <c r="X21" s="148" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Y21" s="151" t="s">
         <v>86</v>
@@ -21328,17 +21330,17 @@
         <v>118</v>
       </c>
       <c r="AC21" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="AD21" s="23" t="s">
         <v>654</v>
-      </c>
-      <c r="AD21" s="23" t="s">
-        <v>655</v>
       </c>
       <c r="AE21" s="23"/>
       <c r="AF21" s="6"/>
       <c r="AG21" s="23"/>
       <c r="AH21" s="43"/>
       <c r="AI21" s="134" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:35" ht="319.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -21353,16 +21355,16 @@
         <v>99</v>
       </c>
       <c r="E22" s="127" t="s">
+        <v>646</v>
+      </c>
+      <c r="F22" s="127" t="s">
         <v>647</v>
-      </c>
-      <c r="F22" s="127" t="s">
-        <v>648</v>
       </c>
       <c r="G22" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I22" s="43" t="s">
         <v>101</v>
@@ -21377,15 +21379,15 @@
         <v>102</v>
       </c>
       <c r="M22" s="76" t="s">
+        <v>661</v>
+      </c>
+      <c r="N22" s="129" t="s">
         <v>662</v>
-      </c>
-      <c r="N22" s="129" t="s">
-        <v>663</v>
       </c>
       <c r="O22" s="129"/>
       <c r="P22" s="46"/>
       <c r="Q22" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R22" s="43" t="s">
         <v>75</v>
@@ -21400,10 +21402,10 @@
       <c r="V22" s="43"/>
       <c r="W22" s="23"/>
       <c r="X22" s="149" t="s">
+        <v>663</v>
+      </c>
+      <c r="Y22" s="151" t="s">
         <v>664</v>
-      </c>
-      <c r="Y22" s="151" t="s">
-        <v>665</v>
       </c>
       <c r="Z22" s="43" t="s">
         <v>49</v>
@@ -21419,7 +21421,7 @@
       <c r="AG22" s="23"/>
       <c r="AH22" s="43"/>
       <c r="AI22" s="134" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="303" customHeight="1" x14ac:dyDescent="0.25">
@@ -21434,16 +21436,16 @@
         <v>99</v>
       </c>
       <c r="E23" s="127" t="s">
+        <v>646</v>
+      </c>
+      <c r="F23" s="127" t="s">
         <v>647</v>
-      </c>
-      <c r="F23" s="127" t="s">
-        <v>648</v>
       </c>
       <c r="G23" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I23" s="43" t="s">
         <v>101</v>
@@ -21458,15 +21460,15 @@
         <v>102</v>
       </c>
       <c r="M23" s="76" t="s">
+        <v>666</v>
+      </c>
+      <c r="N23" s="129" t="s">
         <v>667</v>
-      </c>
-      <c r="N23" s="129" t="s">
-        <v>668</v>
       </c>
       <c r="O23" s="129"/>
       <c r="P23" s="46"/>
       <c r="Q23" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R23" s="43" t="s">
         <v>75</v>
@@ -21481,10 +21483,10 @@
       <c r="V23" s="43"/>
       <c r="W23" s="23"/>
       <c r="X23" s="149" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y23" s="151" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Z23" s="43" t="s">
         <v>49</v>
@@ -21500,7 +21502,7 @@
       <c r="AG23" s="23"/>
       <c r="AH23" s="43"/>
       <c r="AI23" s="134" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -21515,16 +21517,16 @@
         <v>99</v>
       </c>
       <c r="E24" s="46" t="s">
+        <v>646</v>
+      </c>
+      <c r="F24" s="46" t="s">
         <v>647</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>648</v>
       </c>
       <c r="G24" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I24" s="43" t="s">
         <v>101</v>
@@ -21539,15 +21541,15 @@
         <v>102</v>
       </c>
       <c r="M24" s="76" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="7"/>
       <c r="P24" s="117" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="Q24" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R24" s="43"/>
       <c r="S24" s="6"/>
@@ -21561,10 +21563,10 @@
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="AD24" s="23" t="s">
         <v>654</v>
-      </c>
-      <c r="AD24" s="23" t="s">
-        <v>655</v>
       </c>
       <c r="AE24" s="23"/>
       <c r="AF24" s="6"/>
@@ -21586,16 +21588,16 @@
         <v>112</v>
       </c>
       <c r="E25" s="41" t="s">
+        <v>672</v>
+      </c>
+      <c r="F25" s="41" t="s">
         <v>673</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>674</v>
       </c>
       <c r="G25" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H25" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I25" s="43" t="s">
         <v>112</v>
@@ -21610,7 +21612,7 @@
         <v>102</v>
       </c>
       <c r="M25" s="76" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N25" s="43" t="s">
         <v>116</v>
@@ -21618,7 +21620,7 @@
       <c r="O25" s="43"/>
       <c r="P25" s="43"/>
       <c r="Q25" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R25" s="43" t="s">
         <v>62</v>
@@ -21648,10 +21650,10 @@
         <v>118</v>
       </c>
       <c r="AC25" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD25" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD25" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE25" s="23"/>
       <c r="AF25" s="6"/>
@@ -21673,16 +21675,16 @@
         <v>112</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G26" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I26" s="43" t="s">
         <v>112</v>
@@ -21697,7 +21699,7 @@
         <v>102</v>
       </c>
       <c r="M26" s="76" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N26" s="43" t="s">
         <v>122</v>
@@ -21707,7 +21709,7 @@
         <v>123</v>
       </c>
       <c r="Q26" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R26" s="43" t="s">
         <v>62</v>
@@ -21737,10 +21739,10 @@
         <v>118</v>
       </c>
       <c r="AC26" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD26" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD26" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE26" s="23"/>
       <c r="AF26" s="6"/>
@@ -21762,16 +21764,16 @@
         <v>112</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G27" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H27" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I27" s="43" t="s">
         <v>112</v>
@@ -21786,17 +21788,17 @@
         <v>125</v>
       </c>
       <c r="M27" s="76" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N27" s="43" t="s">
         <v>127</v>
       </c>
       <c r="O27" s="43"/>
       <c r="P27" s="51" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="Q27" s="87" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R27" s="43" t="s">
         <v>62</v>
@@ -21826,10 +21828,10 @@
         <v>118</v>
       </c>
       <c r="AC27" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD27" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD27" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE27" s="23"/>
       <c r="AF27" s="6"/>
@@ -21851,16 +21853,16 @@
         <v>112</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G28" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I28" s="43" t="s">
         <v>112</v>
@@ -21875,7 +21877,7 @@
         <v>102</v>
       </c>
       <c r="M28" s="76" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N28" s="43" t="s">
         <v>131</v>
@@ -21885,7 +21887,7 @@
         <v>132</v>
       </c>
       <c r="Q28" s="70" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R28" s="43" t="s">
         <v>62</v>
@@ -21915,10 +21917,10 @@
         <v>118</v>
       </c>
       <c r="AC28" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD28" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD28" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE28" s="23"/>
       <c r="AF28" s="6"/>
@@ -21940,16 +21942,16 @@
         <v>112</v>
       </c>
       <c r="E29" s="128" t="s">
+        <v>683</v>
+      </c>
+      <c r="F29" s="128" t="s">
         <v>684</v>
-      </c>
-      <c r="F29" s="128" t="s">
-        <v>685</v>
       </c>
       <c r="G29" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H29" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I29" s="43" t="s">
         <v>112</v>
@@ -21964,19 +21966,19 @@
         <v>102</v>
       </c>
       <c r="M29" s="76" t="s">
+        <v>685</v>
+      </c>
+      <c r="N29" s="129" t="s">
         <v>686</v>
       </c>
-      <c r="N29" s="129" t="s">
+      <c r="O29" s="129" t="s">
         <v>687</v>
       </c>
-      <c r="O29" s="129" t="s">
+      <c r="P29" s="43" t="s">
         <v>688</v>
       </c>
-      <c r="P29" s="43" t="s">
-        <v>689</v>
-      </c>
       <c r="Q29" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R29" s="43" t="s">
         <v>62</v>
@@ -21995,10 +21997,10 @@
       </c>
       <c r="W29" s="23"/>
       <c r="X29" s="149" t="s">
+        <v>689</v>
+      </c>
+      <c r="Y29" s="151" t="s">
         <v>690</v>
-      </c>
-      <c r="Y29" s="151" t="s">
-        <v>691</v>
       </c>
       <c r="Z29" s="43" t="s">
         <v>49</v>
@@ -22008,17 +22010,17 @@
         <v>118</v>
       </c>
       <c r="AC29" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD29" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD29" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE29" s="23"/>
       <c r="AF29" s="6"/>
       <c r="AG29" s="23"/>
       <c r="AH29" s="43"/>
       <c r="AI29" s="135" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="30" spans="1:35" s="26" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -22035,16 +22037,16 @@
         <v>112</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G30" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I30" s="43" t="s">
         <v>112</v>
@@ -22066,10 +22068,10 @@
       </c>
       <c r="O30" s="43"/>
       <c r="P30" s="51" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="Q30" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R30" s="43" t="s">
         <v>62</v>
@@ -22099,10 +22101,10 @@
         <v>118</v>
       </c>
       <c r="AC30" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD30" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD30" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE30" s="23"/>
       <c r="AF30" s="6"/>
@@ -22124,16 +22126,16 @@
         <v>112</v>
       </c>
       <c r="E31" s="128" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F31" s="128" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G31" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H31" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I31" s="43" t="s">
         <v>112</v>
@@ -22148,19 +22150,19 @@
         <v>102</v>
       </c>
       <c r="M31" s="76" t="s">
+        <v>694</v>
+      </c>
+      <c r="N31" s="129" t="s">
         <v>695</v>
       </c>
-      <c r="N31" s="129" t="s">
+      <c r="O31" s="129" t="s">
         <v>696</v>
       </c>
-      <c r="O31" s="129" t="s">
+      <c r="P31" s="51" t="s">
         <v>697</v>
       </c>
-      <c r="P31" s="51" t="s">
-        <v>698</v>
-      </c>
       <c r="Q31" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R31" s="43" t="s">
         <v>62</v>
@@ -22179,10 +22181,10 @@
       </c>
       <c r="W31" s="23"/>
       <c r="X31" s="149" t="s">
+        <v>698</v>
+      </c>
+      <c r="Y31" s="151" t="s">
         <v>699</v>
-      </c>
-      <c r="Y31" s="151" t="s">
-        <v>700</v>
       </c>
       <c r="Z31" s="43" t="s">
         <v>49</v>
@@ -22192,17 +22194,17 @@
         <v>118</v>
       </c>
       <c r="AC31" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD31" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD31" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE31" s="23"/>
       <c r="AF31" s="6"/>
       <c r="AG31" s="23"/>
       <c r="AH31" s="43"/>
       <c r="AI31" s="135" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="32" spans="1:35" s="26" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
@@ -22219,16 +22221,16 @@
         <v>112</v>
       </c>
       <c r="E32" s="128" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F32" s="128" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G32" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I32" s="43" t="s">
         <v>112</v>
@@ -22243,19 +22245,19 @@
         <v>102</v>
       </c>
       <c r="M32" s="76" t="s">
+        <v>701</v>
+      </c>
+      <c r="N32" s="129" t="s">
         <v>702</v>
       </c>
-      <c r="N32" s="129" t="s">
+      <c r="O32" s="129" t="s">
         <v>703</v>
       </c>
-      <c r="O32" s="129" t="s">
+      <c r="P32" s="43" t="s">
         <v>704</v>
       </c>
-      <c r="P32" s="43" t="s">
-        <v>705</v>
-      </c>
       <c r="Q32" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R32" s="43" t="s">
         <v>62</v>
@@ -22274,10 +22276,10 @@
       </c>
       <c r="W32" s="23"/>
       <c r="X32" s="149" t="s">
+        <v>698</v>
+      </c>
+      <c r="Y32" s="151" t="s">
         <v>699</v>
-      </c>
-      <c r="Y32" s="151" t="s">
-        <v>700</v>
       </c>
       <c r="Z32" s="43" t="s">
         <v>49</v>
@@ -22287,17 +22289,17 @@
         <v>118</v>
       </c>
       <c r="AC32" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD32" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD32" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE32" s="23"/>
       <c r="AF32" s="6"/>
       <c r="AG32" s="23"/>
       <c r="AH32" s="43"/>
       <c r="AI32" s="135" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" spans="1:35" s="26" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -22314,16 +22316,16 @@
         <v>112</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G33" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H33" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I33" s="43" t="s">
         <v>112</v>
@@ -22348,7 +22350,7 @@
         <v>151</v>
       </c>
       <c r="Q33" s="51" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R33" s="43" t="s">
         <v>75</v>
@@ -22378,10 +22380,10 @@
         <v>118</v>
       </c>
       <c r="AC33" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD33" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD33" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE33" s="23"/>
       <c r="AF33" s="6"/>
@@ -22403,16 +22405,16 @@
         <v>112</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G34" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I34" s="43" t="s">
         <v>112</v>
@@ -22434,10 +22436,10 @@
       </c>
       <c r="O34" s="43"/>
       <c r="P34" s="41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q34" s="41" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R34" s="43" t="s">
         <v>75</v>
@@ -22467,10 +22469,10 @@
         <v>118</v>
       </c>
       <c r="AC34" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD34" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD34" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE34" s="23"/>
       <c r="AF34" s="6"/>
@@ -22492,16 +22494,16 @@
         <v>112</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G35" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I35" s="43" t="s">
         <v>112</v>
@@ -22523,10 +22525,10 @@
       </c>
       <c r="O35" s="43"/>
       <c r="P35" s="51" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="Q35" s="51" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R35" s="43" t="s">
         <v>75</v>
@@ -22554,10 +22556,10 @@
       <c r="AA35" s="43"/>
       <c r="AB35" s="23"/>
       <c r="AC35" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD35" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD35" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE35" s="23"/>
       <c r="AF35" s="6"/>
@@ -22579,16 +22581,16 @@
         <v>112</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G36" s="46" t="s">
         <v>114</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I36" s="43" t="s">
         <v>112</v>
@@ -22610,10 +22612,10 @@
       </c>
       <c r="O36" s="48"/>
       <c r="P36" s="71" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="Q36" s="71" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R36" s="43" t="s">
         <v>75</v>
@@ -22641,10 +22643,10 @@
       <c r="AA36" s="43"/>
       <c r="AB36" s="23"/>
       <c r="AC36" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD36" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD36" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE36" s="23"/>
       <c r="AF36" s="6"/>
@@ -22666,16 +22668,16 @@
         <v>112</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G37" s="89" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H37" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I37" s="43" t="s">
         <v>112</v>
@@ -22690,17 +22692,17 @@
         <v>102</v>
       </c>
       <c r="M37" s="76" t="s">
+        <v>710</v>
+      </c>
+      <c r="N37" s="23" t="s">
         <v>711</v>
-      </c>
-      <c r="N37" s="23" t="s">
-        <v>712</v>
       </c>
       <c r="O37" s="90"/>
       <c r="P37" s="109" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q37" s="71" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R37" s="43" t="s">
         <v>75</v>
@@ -22730,10 +22732,10 @@
       <c r="AA37" s="23"/>
       <c r="AB37" s="23"/>
       <c r="AC37" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD37" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD37" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE37" s="23"/>
       <c r="AF37" s="6"/>
@@ -22755,16 +22757,16 @@
         <v>112</v>
       </c>
       <c r="E38" s="128" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F38" s="128" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G38" s="89" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I38" s="43" t="s">
         <v>112</v>
@@ -22779,17 +22781,17 @@
         <v>102</v>
       </c>
       <c r="M38" s="76" t="s">
+        <v>714</v>
+      </c>
+      <c r="N38" s="132" t="s">
         <v>715</v>
-      </c>
-      <c r="N38" s="132" t="s">
-        <v>716</v>
       </c>
       <c r="O38" s="138"/>
       <c r="P38" s="109" t="s">
+        <v>716</v>
+      </c>
+      <c r="Q38" s="71" t="s">
         <v>717</v>
-      </c>
-      <c r="Q38" s="71" t="s">
-        <v>718</v>
       </c>
       <c r="R38" s="43" t="s">
         <v>75</v>
@@ -22810,10 +22812,10 @@
         <v>47</v>
       </c>
       <c r="X38" s="149" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Y38" s="151" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Z38" s="23" t="s">
         <v>49</v>
@@ -22821,17 +22823,17 @@
       <c r="AA38" s="23"/>
       <c r="AB38" s="23"/>
       <c r="AC38" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD38" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD38" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE38" s="23"/>
       <c r="AF38" s="6"/>
       <c r="AG38" s="23"/>
       <c r="AH38" s="23"/>
       <c r="AI38" s="135" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="39" spans="1:35" s="26" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
@@ -22848,16 +22850,16 @@
         <v>112</v>
       </c>
       <c r="E39" s="128" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F39" s="128" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G39" s="89" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H39" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I39" s="43" t="s">
         <v>112</v>
@@ -22872,19 +22874,19 @@
         <v>102</v>
       </c>
       <c r="M39" s="76" t="s">
+        <v>720</v>
+      </c>
+      <c r="N39" s="132" t="s">
         <v>721</v>
       </c>
-      <c r="N39" s="132" t="s">
+      <c r="O39" s="138" t="s">
         <v>722</v>
       </c>
-      <c r="O39" s="138" t="s">
+      <c r="P39" s="109" t="s">
         <v>723</v>
       </c>
-      <c r="P39" s="109" t="s">
-        <v>724</v>
-      </c>
       <c r="Q39" s="71" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="R39" s="43" t="s">
         <v>75</v>
@@ -22905,10 +22907,10 @@
         <v>47</v>
       </c>
       <c r="X39" s="149" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="Y39" s="151" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Z39" s="23" t="s">
         <v>49</v>
@@ -22916,17 +22918,17 @@
       <c r="AA39" s="23"/>
       <c r="AB39" s="23"/>
       <c r="AC39" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD39" s="23" t="s">
         <v>676</v>
-      </c>
-      <c r="AD39" s="23" t="s">
-        <v>677</v>
       </c>
       <c r="AE39" s="23"/>
       <c r="AF39" s="6"/>
       <c r="AG39" s="23"/>
       <c r="AH39" s="23"/>
       <c r="AI39" s="135" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="40" spans="1:35" s="26" customFormat="1" ht="150" hidden="1" x14ac:dyDescent="0.25">
@@ -22952,7 +22954,7 @@
         <v>34</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I40" s="43" t="s">
         <v>167</v>
@@ -23039,19 +23041,19 @@
         <v>53</v>
       </c>
       <c r="D41" s="42" t="s">
+        <v>726</v>
+      </c>
+      <c r="E41" s="129" t="s">
         <v>727</v>
       </c>
-      <c r="E41" s="129" t="s">
+      <c r="F41" s="129" t="s">
         <v>728</v>
-      </c>
-      <c r="F41" s="129" t="s">
-        <v>729</v>
       </c>
       <c r="G41" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H41" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>188</v>
@@ -23067,16 +23069,16 @@
         <v>190</v>
       </c>
       <c r="N41" s="129" t="s">
+        <v>729</v>
+      </c>
+      <c r="O41" s="129" t="s">
         <v>730</v>
-      </c>
-      <c r="O41" s="129" t="s">
-        <v>731</v>
       </c>
       <c r="P41" s="43" t="s">
         <v>192</v>
       </c>
       <c r="Q41" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R41" s="43" t="s">
         <v>43</v>
@@ -23095,10 +23097,10 @@
       </c>
       <c r="W41" s="23"/>
       <c r="X41" s="149" t="s">
+        <v>731</v>
+      </c>
+      <c r="Y41" s="151" t="s">
         <v>732</v>
-      </c>
-      <c r="Y41" s="151" t="s">
-        <v>733</v>
       </c>
       <c r="Z41" s="43" t="s">
         <v>49</v>
@@ -23106,10 +23108,10 @@
       <c r="AA41" s="43"/>
       <c r="AB41" s="23"/>
       <c r="AC41" s="23" t="s">
+        <v>733</v>
+      </c>
+      <c r="AD41" s="23" t="s">
         <v>734</v>
-      </c>
-      <c r="AD41" s="23" t="s">
-        <v>735</v>
       </c>
       <c r="AE41" s="23"/>
       <c r="AF41" s="6"/>
@@ -23118,7 +23120,7 @@
         <v>193</v>
       </c>
       <c r="AI41" s="134" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="42" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -23135,16 +23137,16 @@
         <v>169</v>
       </c>
       <c r="E42" s="129" t="s">
+        <v>736</v>
+      </c>
+      <c r="F42" s="129" t="s">
         <v>737</v>
-      </c>
-      <c r="F42" s="129" t="s">
-        <v>738</v>
       </c>
       <c r="G42" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I42" s="43" t="s">
         <v>171</v>
@@ -23162,16 +23164,16 @@
         <v>172</v>
       </c>
       <c r="N42" s="129" t="s">
+        <v>738</v>
+      </c>
+      <c r="O42" s="139" t="s">
         <v>739</v>
-      </c>
-      <c r="O42" s="139" t="s">
-        <v>740</v>
       </c>
       <c r="P42" s="48" t="s">
         <v>174</v>
       </c>
       <c r="Q42" s="48" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R42" s="43" t="s">
         <v>75</v>
@@ -23190,10 +23192,10 @@
       </c>
       <c r="W42" s="90"/>
       <c r="X42" s="149" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y42" s="151" t="s">
         <v>741</v>
-      </c>
-      <c r="Y42" s="151" t="s">
-        <v>742</v>
       </c>
       <c r="Z42" s="43" t="s">
         <v>49</v>
@@ -23201,7 +23203,7 @@
       <c r="AA42" s="43"/>
       <c r="AB42" s="23"/>
       <c r="AC42" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AD42" s="23" t="s">
         <v>176</v>
@@ -23213,7 +23215,7 @@
         <v>177</v>
       </c>
       <c r="AI42" s="134" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="43" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -23230,16 +23232,16 @@
         <v>169</v>
       </c>
       <c r="E43" s="129" t="s">
+        <v>736</v>
+      </c>
+      <c r="F43" s="129" t="s">
         <v>737</v>
-      </c>
-      <c r="F43" s="129" t="s">
-        <v>738</v>
       </c>
       <c r="G43" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I43" s="43" t="s">
         <v>171</v>
@@ -23254,19 +23256,19 @@
         <v>125</v>
       </c>
       <c r="M43" s="76" t="s">
+        <v>743</v>
+      </c>
+      <c r="N43" s="129" t="s">
         <v>744</v>
       </c>
-      <c r="N43" s="129" t="s">
+      <c r="O43" s="129" t="s">
         <v>745</v>
-      </c>
-      <c r="O43" s="129" t="s">
-        <v>746</v>
       </c>
       <c r="P43" s="43" t="s">
         <v>180</v>
       </c>
       <c r="Q43" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R43" s="43" t="s">
         <v>75</v>
@@ -23285,7 +23287,7 @@
       </c>
       <c r="W43" s="23"/>
       <c r="X43" s="149" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Y43" s="151" t="s">
         <v>86</v>
@@ -23296,7 +23298,7 @@
       <c r="AA43" s="43"/>
       <c r="AB43" s="23"/>
       <c r="AC43" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AD43" s="23" t="s">
         <v>176</v>
@@ -23308,7 +23310,7 @@
         <v>181</v>
       </c>
       <c r="AI43" s="134" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -23323,16 +23325,16 @@
         <v>169</v>
       </c>
       <c r="E44" s="43" t="s">
+        <v>748</v>
+      </c>
+      <c r="F44" s="43" t="s">
         <v>749</v>
-      </c>
-      <c r="F44" s="43" t="s">
-        <v>750</v>
       </c>
       <c r="G44" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I44" s="43" t="s">
         <v>171</v>
@@ -23343,7 +23345,7 @@
       </c>
       <c r="L44" s="43"/>
       <c r="M44" s="76" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N44" s="23"/>
       <c r="O44" s="90"/>
@@ -23361,7 +23363,7 @@
       <c r="AA44" s="23"/>
       <c r="AB44" s="23"/>
       <c r="AC44" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AD44" s="23"/>
       <c r="AE44" s="23"/>
@@ -23384,16 +23386,16 @@
         <v>169</v>
       </c>
       <c r="E45" s="129" t="s">
+        <v>736</v>
+      </c>
+      <c r="F45" s="129" t="s">
         <v>737</v>
-      </c>
-      <c r="F45" s="129" t="s">
-        <v>738</v>
       </c>
       <c r="G45" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H45" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I45" s="43" t="s">
         <v>171</v>
@@ -23408,19 +23410,19 @@
         <v>125</v>
       </c>
       <c r="M45" s="76" t="s">
+        <v>751</v>
+      </c>
+      <c r="N45" s="129" t="s">
         <v>752</v>
       </c>
-      <c r="N45" s="129" t="s">
+      <c r="O45" s="129" t="s">
         <v>753</v>
-      </c>
-      <c r="O45" s="129" t="s">
-        <v>754</v>
       </c>
       <c r="P45" s="43" t="s">
         <v>184</v>
       </c>
       <c r="Q45" s="43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R45" s="43" t="s">
         <v>62</v>
@@ -23437,10 +23439,10 @@
       <c r="V45" s="43"/>
       <c r="W45" s="23"/>
       <c r="X45" s="149" t="s">
+        <v>754</v>
+      </c>
+      <c r="Y45" s="151" t="s">
         <v>755</v>
-      </c>
-      <c r="Y45" s="151" t="s">
-        <v>756</v>
       </c>
       <c r="Z45" s="43" t="s">
         <v>49</v>
@@ -23448,7 +23450,7 @@
       <c r="AA45" s="43"/>
       <c r="AB45" s="23"/>
       <c r="AC45" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AD45" s="23" t="s">
         <v>176</v>
@@ -23460,7 +23462,7 @@
         <v>181</v>
       </c>
       <c r="AI45" s="134" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="46" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -23474,19 +23476,19 @@
         <v>53</v>
       </c>
       <c r="D46" s="42" t="s">
+        <v>757</v>
+      </c>
+      <c r="E46" s="43" t="s">
         <v>758</v>
       </c>
-      <c r="E46" s="43" t="s">
+      <c r="F46" s="43" t="s">
         <v>759</v>
-      </c>
-      <c r="F46" s="43" t="s">
-        <v>760</v>
       </c>
       <c r="G46" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I46" s="43" t="s">
         <v>188</v>
@@ -23508,7 +23510,7 @@
       </c>
       <c r="O46" s="43"/>
       <c r="P46" s="43" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q46" s="43" t="s">
         <v>201</v>
@@ -23541,10 +23543,10 @@
       </c>
       <c r="AB46" s="23"/>
       <c r="AC46" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AD46" s="23" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AE46" s="23"/>
       <c r="AF46" s="6"/>
@@ -23563,19 +23565,19 @@
         <v>53</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E47" s="129" t="s">
+        <v>762</v>
+      </c>
+      <c r="F47" s="129" t="s">
         <v>763</v>
-      </c>
-      <c r="F47" s="129" t="s">
-        <v>764</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="46" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I47" s="43" t="s">
         <v>188</v>
@@ -23588,13 +23590,13 @@
       </c>
       <c r="L47" s="43"/>
       <c r="M47" s="76" t="s">
+        <v>765</v>
+      </c>
+      <c r="N47" s="129" t="s">
         <v>766</v>
       </c>
-      <c r="N47" s="129" t="s">
+      <c r="O47" s="129" t="s">
         <v>767</v>
-      </c>
-      <c r="O47" s="129" t="s">
-        <v>768</v>
       </c>
       <c r="P47" s="43"/>
       <c r="Q47" s="43" t="s">
@@ -23619,7 +23621,7 @@
         <v>201</v>
       </c>
       <c r="X47" s="149" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="Y47" s="151" t="s">
         <v>86</v>
@@ -23636,7 +23638,7 @@
         <v>205</v>
       </c>
       <c r="AI47" s="134" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="48" spans="1:35" ht="281.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -23648,19 +23650,19 @@
         <v>53</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E48" s="129" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F48" s="129" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G48" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I48" s="43" t="s">
         <v>188</v>
@@ -23673,13 +23675,13 @@
       </c>
       <c r="L48" s="43"/>
       <c r="M48" s="76" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="N48" s="129" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O48" s="129" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P48" s="43"/>
       <c r="Q48" s="43" t="s">
@@ -23704,7 +23706,7 @@
         <v>201</v>
       </c>
       <c r="X48" s="149" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Y48" s="151" t="s">
         <v>86</v>
@@ -23721,7 +23723,7 @@
         <v>205</v>
       </c>
       <c r="AI48" s="134" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="49" spans="1:35" s="105" customFormat="1" ht="390" x14ac:dyDescent="0.25">
@@ -23729,23 +23731,23 @@
         <v>206</v>
       </c>
       <c r="B49" s="103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C49" s="103"/>
       <c r="D49" s="126" t="s">
         <v>207</v>
       </c>
       <c r="E49" s="128" t="s">
+        <v>773</v>
+      </c>
+      <c r="F49" s="128" t="s">
         <v>774</v>
-      </c>
-      <c r="F49" s="128" t="s">
-        <v>775</v>
       </c>
       <c r="G49" s="104" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="104" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I49" s="41" t="s">
         <v>209</v>
@@ -23763,10 +23765,10 @@
         <v>211</v>
       </c>
       <c r="N49" s="128" t="s">
+        <v>775</v>
+      </c>
+      <c r="O49" s="128" t="s">
         <v>776</v>
-      </c>
-      <c r="O49" s="128" t="s">
-        <v>777</v>
       </c>
       <c r="P49" s="41" t="s">
         <v>213</v>
@@ -23789,10 +23791,10 @@
       </c>
       <c r="W49" s="95"/>
       <c r="X49" s="149" t="s">
+        <v>777</v>
+      </c>
+      <c r="Y49" s="151" t="s">
         <v>778</v>
-      </c>
-      <c r="Y49" s="151" t="s">
-        <v>779</v>
       </c>
       <c r="Z49" s="41" t="s">
         <v>49</v>
@@ -23806,7 +23808,7 @@
       <c r="AG49" s="95"/>
       <c r="AH49" s="41"/>
       <c r="AI49" s="136" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="50" spans="1:35" s="105" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
@@ -23814,7 +23816,7 @@
         <v>206</v>
       </c>
       <c r="B50" s="103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C50" s="103" t="s">
         <v>53</v>
@@ -23823,16 +23825,16 @@
         <v>207</v>
       </c>
       <c r="E50" s="128" t="s">
+        <v>773</v>
+      </c>
+      <c r="F50" s="128" t="s">
         <v>774</v>
-      </c>
-      <c r="F50" s="128" t="s">
-        <v>775</v>
       </c>
       <c r="G50" s="104" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="104" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I50" s="41" t="s">
         <v>209</v>
@@ -23850,10 +23852,10 @@
         <v>207</v>
       </c>
       <c r="N50" s="128" t="s">
+        <v>780</v>
+      </c>
+      <c r="O50" s="128" t="s">
         <v>781</v>
-      </c>
-      <c r="O50" s="128" t="s">
-        <v>782</v>
       </c>
       <c r="P50" s="41" t="s">
         <v>219</v>
@@ -23876,10 +23878,10 @@
       </c>
       <c r="W50" s="95"/>
       <c r="X50" s="149" t="s">
+        <v>782</v>
+      </c>
+      <c r="Y50" s="151" t="s">
         <v>783</v>
-      </c>
-      <c r="Y50" s="151" t="s">
-        <v>784</v>
       </c>
       <c r="Z50" s="41" t="s">
         <v>49</v>
@@ -23895,7 +23897,7 @@
       <c r="AG50" s="95"/>
       <c r="AH50" s="41"/>
       <c r="AI50" s="136" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="51" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -23903,7 +23905,7 @@
         <v>225</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C51" s="45" t="s">
         <v>98</v>
@@ -23912,16 +23914,16 @@
         <v>226</v>
       </c>
       <c r="E51" s="130" t="s">
+        <v>785</v>
+      </c>
+      <c r="F51" s="130" t="s">
         <v>786</v>
-      </c>
-      <c r="F51" s="130" t="s">
-        <v>787</v>
       </c>
       <c r="G51" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H51" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I51" s="43" t="s">
         <v>226</v>
@@ -23936,19 +23938,19 @@
         <v>102</v>
       </c>
       <c r="M51" s="76" t="s">
+        <v>787</v>
+      </c>
+      <c r="N51" s="129" t="s">
         <v>788</v>
       </c>
-      <c r="N51" s="129" t="s">
+      <c r="O51" s="129" t="s">
         <v>789</v>
       </c>
-      <c r="O51" s="129" t="s">
+      <c r="P51" s="43" t="s">
         <v>790</v>
       </c>
-      <c r="P51" s="43" t="s">
-        <v>791</v>
-      </c>
       <c r="Q51" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R51" s="43" t="s">
         <v>62</v>
@@ -23963,7 +23965,7 @@
       </c>
       <c r="W51" s="6"/>
       <c r="X51" s="149" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="Y51" s="151" t="s">
         <v>86</v>
@@ -23974,7 +23976,7 @@
       <c r="AA51" s="43"/>
       <c r="AB51" s="6"/>
       <c r="AC51" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AD51" s="6" t="s">
         <v>231</v>
@@ -23985,10 +23987,10 @@
       </c>
       <c r="AG51" s="6"/>
       <c r="AH51" s="43" t="s">
+        <v>793</v>
+      </c>
+      <c r="AI51" s="134" t="s">
         <v>794</v>
-      </c>
-      <c r="AI51" s="134" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="52" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -23996,7 +23998,7 @@
         <v>225</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C52" s="45" t="s">
         <v>98</v>
@@ -24005,10 +24007,10 @@
         <v>226</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G52" s="46" t="s">
         <v>55</v>
@@ -24037,7 +24039,7 @@
         <v>235</v>
       </c>
       <c r="Q52" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R52" s="43" t="s">
         <v>62</v>
@@ -24061,7 +24063,7 @@
       <c r="AA52" s="43"/>
       <c r="AB52" s="6"/>
       <c r="AC52" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AD52" s="6" t="s">
         <v>236</v>
@@ -24079,7 +24081,7 @@
         <v>225</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C53" s="45" t="s">
         <v>98</v>
@@ -24088,10 +24090,10 @@
         <v>226</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G53" s="46" t="s">
         <v>55</v>
@@ -24120,7 +24122,7 @@
         <v>239</v>
       </c>
       <c r="Q53" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R53" s="43" t="s">
         <v>62</v>
@@ -24144,7 +24146,7 @@
       <c r="AA53" s="43"/>
       <c r="AB53" s="6"/>
       <c r="AC53" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AD53" s="6" t="s">
         <v>240</v>
@@ -24162,7 +24164,7 @@
         <v>225</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C54" s="45" t="s">
         <v>98</v>
@@ -24171,10 +24173,10 @@
         <v>226</v>
       </c>
       <c r="E54" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G54" s="46" t="s">
         <v>55</v>
@@ -24225,7 +24227,7 @@
       <c r="AA54" s="43"/>
       <c r="AB54" s="6"/>
       <c r="AC54" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AD54" s="6" t="s">
         <v>244</v>
@@ -24243,7 +24245,7 @@
         <v>206</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C55" s="45" t="s">
         <v>31</v>
@@ -24252,16 +24254,16 @@
         <v>245</v>
       </c>
       <c r="E55" s="129" t="s">
+        <v>796</v>
+      </c>
+      <c r="F55" s="129" t="s">
         <v>797</v>
-      </c>
-      <c r="F55" s="129" t="s">
-        <v>798</v>
       </c>
       <c r="G55" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I55" s="43" t="s">
         <v>245</v>
@@ -24279,10 +24281,10 @@
         <v>245</v>
       </c>
       <c r="N55" s="129" t="s">
+        <v>798</v>
+      </c>
+      <c r="O55" s="129" t="s">
         <v>799</v>
-      </c>
-      <c r="O55" s="129" t="s">
-        <v>800</v>
       </c>
       <c r="P55" s="43" t="s">
         <v>249</v>
@@ -24303,10 +24305,10 @@
       </c>
       <c r="W55" s="6"/>
       <c r="X55" s="149" t="s">
+        <v>800</v>
+      </c>
+      <c r="Y55" s="151" t="s">
         <v>801</v>
-      </c>
-      <c r="Y55" s="151" t="s">
-        <v>802</v>
       </c>
       <c r="Z55" s="43" t="s">
         <v>203</v>
@@ -24314,7 +24316,7 @@
       <c r="AA55" s="43"/>
       <c r="AB55" s="6"/>
       <c r="AC55" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="AD55" s="6"/>
       <c r="AE55" s="6"/>
@@ -24324,7 +24326,7 @@
         <v>252</v>
       </c>
       <c r="AI55" s="134" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="56" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -24332,7 +24334,7 @@
         <v>111</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C56" s="45" t="s">
         <v>31</v>
@@ -24341,16 +24343,16 @@
         <v>254</v>
       </c>
       <c r="E56" s="129" t="s">
+        <v>804</v>
+      </c>
+      <c r="F56" s="129" t="s">
         <v>805</v>
-      </c>
-      <c r="F56" s="129" t="s">
-        <v>806</v>
       </c>
       <c r="G56" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I56" s="43" t="s">
         <v>37</v>
@@ -24363,14 +24365,14 @@
       </c>
       <c r="L56" s="43"/>
       <c r="M56" s="76" t="s">
+        <v>806</v>
+      </c>
+      <c r="N56" s="129" t="s">
         <v>807</v>
-      </c>
-      <c r="N56" s="129" t="s">
-        <v>808</v>
       </c>
       <c r="O56" s="129"/>
       <c r="P56" s="43" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="Q56" s="43"/>
       <c r="R56" s="43" t="s">
@@ -24388,16 +24390,16 @@
         <v>47</v>
       </c>
       <c r="X56" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y56" s="151" t="s">
         <v>810</v>
-      </c>
-      <c r="Y56" s="151" t="s">
-        <v>811</v>
       </c>
       <c r="Z56" s="43"/>
       <c r="AA56" s="43"/>
       <c r="AB56" s="6"/>
       <c r="AC56" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD56" s="6"/>
       <c r="AE56" s="6"/>
@@ -24409,7 +24411,7 @@
         <v>259</v>
       </c>
       <c r="AI56" s="134" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="57" spans="1:35" ht="405" x14ac:dyDescent="0.25">
@@ -24417,7 +24419,7 @@
         <v>111</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C57" s="45" t="s">
         <v>31</v>
@@ -24426,16 +24428,16 @@
         <v>254</v>
       </c>
       <c r="E57" s="129" t="s">
+        <v>804</v>
+      </c>
+      <c r="F57" s="129" t="s">
         <v>805</v>
-      </c>
-      <c r="F57" s="129" t="s">
-        <v>806</v>
       </c>
       <c r="G57" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I57" s="43" t="s">
         <v>260</v>
@@ -24451,10 +24453,10 @@
         <v>375</v>
       </c>
       <c r="N57" s="129" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="O57" s="129" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P57" s="43"/>
       <c r="Q57" s="43"/>
@@ -24471,10 +24473,10 @@
       </c>
       <c r="W57" s="6"/>
       <c r="X57" s="148" t="s">
+        <v>580</v>
+      </c>
+      <c r="Y57" s="151" t="s">
         <v>581</v>
-      </c>
-      <c r="Y57" s="151" t="s">
-        <v>582</v>
       </c>
       <c r="Z57" s="43" t="s">
         <v>49</v>
@@ -24482,7 +24484,7 @@
       <c r="AA57" s="43"/>
       <c r="AB57" s="6"/>
       <c r="AC57" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD57" s="6"/>
       <c r="AE57" s="6"/>
@@ -24492,7 +24494,7 @@
         <v>259</v>
       </c>
       <c r="AI57" s="134" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="58" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -24500,7 +24502,7 @@
         <v>111</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C58" s="45" t="s">
         <v>31</v>
@@ -24509,10 +24511,10 @@
         <v>254</v>
       </c>
       <c r="E58" s="43" t="s">
+        <v>814</v>
+      </c>
+      <c r="F58" s="43" t="s">
         <v>815</v>
-      </c>
-      <c r="F58" s="43" t="s">
-        <v>816</v>
       </c>
       <c r="G58" s="46" t="s">
         <v>34</v>
@@ -24529,14 +24531,14 @@
       </c>
       <c r="L58" s="43"/>
       <c r="M58" s="76" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="N58" s="43" t="s">
         <v>267</v>
       </c>
       <c r="O58" s="43"/>
       <c r="P58" s="43" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q58" s="43"/>
       <c r="R58" s="43" t="s">
@@ -24559,7 +24561,7 @@
       <c r="AA58" s="43"/>
       <c r="AB58" s="6"/>
       <c r="AC58" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD58" s="6" t="s">
         <v>271</v>
@@ -24577,23 +24579,23 @@
         <v>111</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="42" t="s">
         <v>254</v>
       </c>
       <c r="E59" s="129" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F59" s="129" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G59" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H59" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I59" s="43" t="s">
         <v>265</v>
@@ -24606,14 +24608,14 @@
       </c>
       <c r="L59" s="43"/>
       <c r="M59" s="76" t="s">
+        <v>818</v>
+      </c>
+      <c r="N59" s="133" t="s">
         <v>819</v>
-      </c>
-      <c r="N59" s="133" t="s">
-        <v>820</v>
       </c>
       <c r="O59" s="140"/>
       <c r="P59" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q59" s="43"/>
       <c r="R59" s="43"/>
@@ -24621,22 +24623,22 @@
       <c r="T59" s="6"/>
       <c r="U59" s="6"/>
       <c r="V59" s="43" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="W59" s="7"/>
       <c r="X59" s="148" t="s">
+        <v>822</v>
+      </c>
+      <c r="Y59" s="151" t="s">
         <v>823</v>
-      </c>
-      <c r="Y59" s="151" t="s">
-        <v>824</v>
       </c>
       <c r="Z59" s="6"/>
       <c r="AA59" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AB59" s="6"/>
       <c r="AC59" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD59" s="6"/>
       <c r="AE59" s="6"/>
@@ -24644,7 +24646,7 @@
       <c r="AG59" s="6"/>
       <c r="AH59" s="6"/>
       <c r="AI59" s="134" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="60" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -24652,17 +24654,17 @@
         <v>111</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="42" t="s">
         <v>254</v>
       </c>
       <c r="E60" s="43" t="s">
+        <v>814</v>
+      </c>
+      <c r="F60" s="43" t="s">
         <v>815</v>
-      </c>
-      <c r="F60" s="43" t="s">
-        <v>816</v>
       </c>
       <c r="G60" s="46" t="s">
         <v>34</v>
@@ -24679,12 +24681,12 @@
       </c>
       <c r="L60" s="43"/>
       <c r="M60" s="76" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="N60" s="6"/>
       <c r="O60" s="7"/>
       <c r="P60" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q60" s="43"/>
       <c r="R60" s="43"/>
@@ -24692,7 +24694,7 @@
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
       <c r="V60" s="43" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="W60" s="7"/>
       <c r="X60" s="120"/>
@@ -24701,7 +24703,7 @@
       <c r="AA60" s="6"/>
       <c r="AB60" s="6"/>
       <c r="AC60" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD60" s="6"/>
       <c r="AE60" s="6"/>
@@ -24715,23 +24717,23 @@
         <v>111</v>
       </c>
       <c r="B61" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="42" t="s">
         <v>254</v>
       </c>
       <c r="E61" s="129" t="s">
+        <v>804</v>
+      </c>
+      <c r="F61" s="129" t="s">
         <v>805</v>
-      </c>
-      <c r="F61" s="129" t="s">
-        <v>806</v>
       </c>
       <c r="G61" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H61" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I61" s="43" t="s">
         <v>265</v>
@@ -24740,17 +24742,17 @@
         <v>37</v>
       </c>
       <c r="K61" s="43" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L61" s="43"/>
       <c r="M61" s="76" t="s">
+        <v>827</v>
+      </c>
+      <c r="N61" s="133" t="s">
         <v>828</v>
       </c>
-      <c r="N61" s="133" t="s">
+      <c r="O61" s="140" t="s">
         <v>829</v>
-      </c>
-      <c r="O61" s="140" t="s">
-        <v>830</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="43"/>
@@ -24759,14 +24761,14 @@
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
       <c r="V61" s="43" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="W61" s="7"/>
       <c r="X61" s="148" t="s">
+        <v>830</v>
+      </c>
+      <c r="Y61" s="151" t="s">
         <v>831</v>
-      </c>
-      <c r="Y61" s="151" t="s">
-        <v>832</v>
       </c>
       <c r="Z61" s="6" t="s">
         <v>49</v>
@@ -24774,7 +24776,7 @@
       <c r="AA61" s="6"/>
       <c r="AB61" s="6"/>
       <c r="AC61" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD61" s="6"/>
       <c r="AE61" s="6"/>
@@ -24782,7 +24784,7 @@
       <c r="AG61" s="6"/>
       <c r="AH61" s="6"/>
       <c r="AI61" s="134" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="62" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -24790,17 +24792,17 @@
         <v>111</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="42" t="s">
         <v>254</v>
       </c>
       <c r="E62" s="43" t="s">
+        <v>814</v>
+      </c>
+      <c r="F62" s="43" t="s">
         <v>815</v>
-      </c>
-      <c r="F62" s="43" t="s">
-        <v>816</v>
       </c>
       <c r="G62" s="46" t="s">
         <v>34</v>
@@ -24815,7 +24817,7 @@
       <c r="K62" s="43"/>
       <c r="L62" s="43"/>
       <c r="M62" s="102" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N62" s="6"/>
       <c r="O62" s="7"/>
@@ -24826,11 +24828,11 @@
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
       <c r="V62" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="W62" s="7"/>
       <c r="X62" s="120" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Y62" s="120"/>
       <c r="Z62" s="6" t="s">
@@ -24839,16 +24841,16 @@
       <c r="AA62" s="6"/>
       <c r="AB62" s="6"/>
       <c r="AC62" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD62" s="6"/>
       <c r="AE62" s="6"/>
       <c r="AF62" s="6"/>
       <c r="AG62" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="AH62" s="6" t="s">
         <v>836</v>
-      </c>
-      <c r="AH62" s="6" t="s">
-        <v>837</v>
       </c>
       <c r="AI62" s="1"/>
     </row>
@@ -24857,7 +24859,7 @@
         <v>272</v>
       </c>
       <c r="B63" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C63" s="45" t="s">
         <v>273</v>
@@ -24866,16 +24868,16 @@
         <v>274</v>
       </c>
       <c r="E63" s="129" t="s">
+        <v>837</v>
+      </c>
+      <c r="F63" s="129" t="s">
         <v>838</v>
-      </c>
-      <c r="F63" s="129" t="s">
-        <v>839</v>
       </c>
       <c r="G63" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I63" s="43" t="s">
         <v>276</v>
@@ -24893,16 +24895,16 @@
         <v>278</v>
       </c>
       <c r="N63" s="129" t="s">
+        <v>839</v>
+      </c>
+      <c r="O63" s="129" t="s">
         <v>840</v>
       </c>
-      <c r="O63" s="129" t="s">
+      <c r="P63" s="98" t="s">
         <v>841</v>
       </c>
-      <c r="P63" s="98" t="s">
-        <v>842</v>
-      </c>
       <c r="Q63" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R63" s="43" t="s">
         <v>44</v>
@@ -24917,7 +24919,7 @@
       <c r="V63" s="43"/>
       <c r="W63" s="6"/>
       <c r="X63" s="148" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Y63" s="151" t="s">
         <v>86</v>
@@ -24926,7 +24928,7 @@
       <c r="AA63" s="43"/>
       <c r="AB63" s="6"/>
       <c r="AC63" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD63" s="6"/>
       <c r="AE63" s="6"/>
@@ -24936,7 +24938,7 @@
         <v>281</v>
       </c>
       <c r="AI63" s="134" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="64" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -24944,7 +24946,7 @@
         <v>272</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>273</v>
@@ -24953,16 +24955,16 @@
         <v>274</v>
       </c>
       <c r="E64" s="129" t="s">
+        <v>837</v>
+      </c>
+      <c r="F64" s="129" t="s">
         <v>838</v>
-      </c>
-      <c r="F64" s="129" t="s">
-        <v>839</v>
       </c>
       <c r="G64" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I64" s="43" t="s">
         <v>276</v>
@@ -24980,16 +24982,16 @@
         <v>283</v>
       </c>
       <c r="N64" s="129" t="s">
+        <v>845</v>
+      </c>
+      <c r="O64" s="129" t="s">
         <v>846</v>
       </c>
-      <c r="O64" s="129" t="s">
+      <c r="P64" s="43" t="s">
         <v>847</v>
       </c>
-      <c r="P64" s="43" t="s">
-        <v>848</v>
-      </c>
       <c r="Q64" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R64" s="43" t="s">
         <v>44</v>
@@ -25004,23 +25006,23 @@
       <c r="V64" s="43"/>
       <c r="W64" s="6"/>
       <c r="X64" s="148" t="s">
+        <v>586</v>
+      </c>
+      <c r="Y64" s="151" t="s">
         <v>587</v>
-      </c>
-      <c r="Y64" s="151" t="s">
-        <v>588</v>
       </c>
       <c r="Z64" s="43"/>
       <c r="AA64" s="43"/>
       <c r="AB64" s="6"/>
       <c r="AC64" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD64" s="6"/>
       <c r="AE64" s="1"/>
       <c r="AG64" s="6"/>
       <c r="AH64" s="43"/>
       <c r="AI64" s="134" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="65" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -25028,7 +25030,7 @@
         <v>272</v>
       </c>
       <c r="B65" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C65" s="45" t="s">
         <v>273</v>
@@ -25037,16 +25039,16 @@
         <v>274</v>
       </c>
       <c r="E65" s="43" t="s">
+        <v>849</v>
+      </c>
+      <c r="F65" s="43" t="s">
         <v>850</v>
-      </c>
-      <c r="F65" s="43" t="s">
-        <v>851</v>
       </c>
       <c r="G65" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I65" s="43" t="s">
         <v>276</v>
@@ -25068,10 +25070,10 @@
       </c>
       <c r="O65" s="43"/>
       <c r="P65" s="43" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q65" s="43" t="s">
         <v>852</v>
-      </c>
-      <c r="Q65" s="43" t="s">
-        <v>853</v>
       </c>
       <c r="R65" s="43" t="s">
         <v>106</v>
@@ -25093,7 +25095,7 @@
       <c r="AA65" s="43"/>
       <c r="AB65" s="6"/>
       <c r="AC65" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD65" s="6"/>
       <c r="AE65" s="6"/>
@@ -25107,7 +25109,7 @@
         <v>272</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>273</v>
@@ -25116,16 +25118,16 @@
         <v>274</v>
       </c>
       <c r="E66" s="129" t="s">
+        <v>837</v>
+      </c>
+      <c r="F66" s="129" t="s">
         <v>838</v>
-      </c>
-      <c r="F66" s="129" t="s">
-        <v>839</v>
       </c>
       <c r="G66" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I66" s="43" t="s">
         <v>276</v>
@@ -25140,19 +25142,19 @@
         <v>102</v>
       </c>
       <c r="M66" s="76" t="s">
+        <v>853</v>
+      </c>
+      <c r="N66" s="129" t="s">
         <v>854</v>
       </c>
-      <c r="N66" s="129" t="s">
+      <c r="O66" s="129" t="s">
         <v>855</v>
       </c>
-      <c r="O66" s="129" t="s">
+      <c r="P66" s="43" t="s">
         <v>856</v>
       </c>
-      <c r="P66" s="43" t="s">
+      <c r="Q66" s="43" t="s">
         <v>857</v>
-      </c>
-      <c r="Q66" s="43" t="s">
-        <v>858</v>
       </c>
       <c r="R66" s="43" t="s">
         <v>106</v>
@@ -25167,7 +25169,7 @@
       <c r="V66" s="43"/>
       <c r="W66" s="6"/>
       <c r="X66" s="152" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="Y66" s="151" t="s">
         <v>86</v>
@@ -25176,7 +25178,7 @@
       <c r="AA66" s="43"/>
       <c r="AB66" s="6"/>
       <c r="AC66" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD66" s="6"/>
       <c r="AE66" s="6"/>
@@ -25184,7 +25186,7 @@
       <c r="AG66" s="6"/>
       <c r="AH66" s="43"/>
       <c r="AI66" s="134" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="67" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -25201,16 +25203,16 @@
         <v>274</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F67" s="51" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G67" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H67" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I67" s="43" t="s">
         <v>276</v>
@@ -25232,10 +25234,10 @@
       </c>
       <c r="O67" s="48"/>
       <c r="P67" s="48" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q67" s="48" t="s">
         <v>862</v>
-      </c>
-      <c r="Q67" s="48" t="s">
-        <v>863</v>
       </c>
       <c r="R67" s="43" t="s">
         <v>106</v>
@@ -25261,7 +25263,7 @@
       <c r="AA67" s="43"/>
       <c r="AB67" s="23"/>
       <c r="AC67" s="23" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD67" s="23" t="s">
         <v>295</v>
@@ -25277,7 +25279,7 @@
         <v>272</v>
       </c>
       <c r="B68" s="103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C68" s="103" t="s">
         <v>273</v>
@@ -25286,16 +25288,16 @@
         <v>274</v>
       </c>
       <c r="E68" s="51" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F68" s="51" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G68" s="104" t="s">
         <v>34</v>
       </c>
       <c r="H68" s="104" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I68" s="41" t="s">
         <v>276</v>
@@ -25334,7 +25336,7 @@
       <c r="AA68" s="41"/>
       <c r="AB68" s="95"/>
       <c r="AC68" s="95" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AD68" s="95" t="s">
         <v>295</v>
@@ -25350,7 +25352,7 @@
         <v>272</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="45" t="s">
         <v>273</v>
@@ -25359,16 +25361,16 @@
         <v>274</v>
       </c>
       <c r="E69" s="129" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F69" s="129" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G69" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I69" s="43" t="s">
         <v>276</v>
@@ -25384,10 +25386,10 @@
         <v>301</v>
       </c>
       <c r="N69" s="129" t="s">
+        <v>865</v>
+      </c>
+      <c r="O69" s="129" t="s">
         <v>866</v>
-      </c>
-      <c r="O69" s="129" t="s">
-        <v>867</v>
       </c>
       <c r="P69" s="43"/>
       <c r="Q69" s="43"/>
@@ -25400,16 +25402,16 @@
       <c r="V69" s="43"/>
       <c r="W69" s="6"/>
       <c r="X69" s="148" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y69" s="153" t="s">
         <v>868</v>
-      </c>
-      <c r="Y69" s="153" t="s">
-        <v>869</v>
       </c>
       <c r="Z69" s="43"/>
       <c r="AA69" s="43"/>
       <c r="AB69" s="6"/>
       <c r="AC69" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AD69" s="6" t="s">
         <v>295</v>
@@ -25419,7 +25421,7 @@
       <c r="AG69" s="6"/>
       <c r="AH69" s="43"/>
       <c r="AI69" s="134" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="70" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -25427,7 +25429,7 @@
         <v>111</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C70" s="45" t="s">
         <v>31</v>
@@ -25436,10 +25438,10 @@
         <v>305</v>
       </c>
       <c r="E70" s="43" t="s">
+        <v>870</v>
+      </c>
+      <c r="F70" s="43" t="s">
         <v>871</v>
-      </c>
-      <c r="F70" s="43" t="s">
-        <v>872</v>
       </c>
       <c r="G70" s="46" t="s">
         <v>34</v>
@@ -25458,7 +25460,7 @@
         <v>198</v>
       </c>
       <c r="M70" s="76" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="N70" s="43" t="s">
         <v>37</v>
@@ -25486,7 +25488,7 @@
       <c r="AA70" s="43"/>
       <c r="AB70" s="6"/>
       <c r="AC70" s="6" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AD70" s="6"/>
       <c r="AE70" s="6"/>
@@ -25604,7 +25606,7 @@
       <c r="AA72" s="6"/>
       <c r="AB72" s="6"/>
       <c r="AC72" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AD72" s="6"/>
       <c r="AE72" s="6"/>
@@ -25646,7 +25648,7 @@
       <c r="N73" s="43"/>
       <c r="O73" s="43"/>
       <c r="P73" s="43" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="Q73" s="43"/>
       <c r="R73" s="43"/>
@@ -25661,7 +25663,7 @@
       <c r="AA73" s="6"/>
       <c r="AB73" s="6"/>
       <c r="AC73" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AD73" s="6"/>
       <c r="AE73" s="6"/>
@@ -25684,16 +25686,16 @@
         <v>341</v>
       </c>
       <c r="E74" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F74" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G74" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H74" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I74" s="43" t="s">
         <v>343</v>
@@ -25711,7 +25713,7 @@
         <v>344</v>
       </c>
       <c r="N74" s="43" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O74" s="43"/>
       <c r="P74" s="43"/>
@@ -25742,7 +25744,7 @@
       <c r="AA74" s="43"/>
       <c r="AB74" s="23"/>
       <c r="AC74" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD74" s="23" t="s">
         <v>346</v>
@@ -25767,16 +25769,16 @@
         <v>341</v>
       </c>
       <c r="E75" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F75" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G75" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H75" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I75" s="43" t="s">
         <v>343</v>
@@ -25792,7 +25794,7 @@
         <v>286</v>
       </c>
       <c r="N75" s="43" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="O75" s="43"/>
       <c r="P75" s="43"/>
@@ -25819,7 +25821,7 @@
       <c r="AA75" s="43"/>
       <c r="AB75" s="23"/>
       <c r="AC75" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD75" s="23" t="s">
         <v>346</v>
@@ -25842,16 +25844,16 @@
         <v>341</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G76" s="46" t="s">
         <v>55</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I76" s="43" t="s">
         <v>343</v>
@@ -25864,14 +25866,14 @@
         <v>102</v>
       </c>
       <c r="M76" s="76" t="s">
+        <v>881</v>
+      </c>
+      <c r="N76" s="43" t="s">
         <v>882</v>
-      </c>
-      <c r="N76" s="43" t="s">
-        <v>883</v>
       </c>
       <c r="O76" s="43"/>
       <c r="P76" s="43" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="Q76" s="43"/>
       <c r="R76" s="43"/>
@@ -25896,7 +25898,7 @@
       <c r="AA76" s="23"/>
       <c r="AB76" s="23"/>
       <c r="AC76" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD76" s="23"/>
       <c r="AE76" s="23"/>
@@ -25919,10 +25921,10 @@
         <v>341</v>
       </c>
       <c r="E77" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F77" s="43" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G77" s="46" t="s">
         <v>55</v>
@@ -25944,11 +25946,11 @@
         <v>349</v>
       </c>
       <c r="N77" s="43" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O77" s="43"/>
       <c r="P77" s="43" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="Q77" s="43"/>
       <c r="R77" s="43" t="s">
@@ -25973,7 +25975,7 @@
       <c r="AA77" s="43"/>
       <c r="AB77" s="43"/>
       <c r="AC77" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD77" s="23"/>
       <c r="AE77" s="23"/>
@@ -25994,16 +25996,16 @@
         <v>341</v>
       </c>
       <c r="E78" s="129" t="s">
+        <v>886</v>
+      </c>
+      <c r="F78" s="129" t="s">
         <v>887</v>
-      </c>
-      <c r="F78" s="129" t="s">
-        <v>888</v>
       </c>
       <c r="G78" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I78" s="43" t="s">
         <v>343</v>
@@ -26018,10 +26020,10 @@
         <v>102</v>
       </c>
       <c r="M78" s="76" t="s">
+        <v>888</v>
+      </c>
+      <c r="N78" s="129" t="s">
         <v>889</v>
-      </c>
-      <c r="N78" s="129" t="s">
-        <v>890</v>
       </c>
       <c r="O78" s="129"/>
       <c r="P78" s="43"/>
@@ -26033,7 +26035,7 @@
       <c r="V78" s="43"/>
       <c r="W78" s="23"/>
       <c r="X78" s="148" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Y78" s="151" t="s">
         <v>86</v>
@@ -26048,7 +26050,7 @@
       <c r="AG78" s="23"/>
       <c r="AH78" s="23"/>
       <c r="AI78" s="134" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="79" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -26065,16 +26067,16 @@
         <v>341</v>
       </c>
       <c r="E79" s="129" t="s">
+        <v>886</v>
+      </c>
+      <c r="F79" s="129" t="s">
         <v>887</v>
-      </c>
-      <c r="F79" s="129" t="s">
-        <v>888</v>
       </c>
       <c r="G79" s="46" t="s">
         <v>351</v>
       </c>
       <c r="H79" s="46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I79" s="43" t="s">
         <v>343</v>
@@ -26092,7 +26094,7 @@
         <v>352</v>
       </c>
       <c r="N79" s="129" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="O79" s="139"/>
       <c r="P79" s="48" t="s">
@@ -26116,7 +26118,7 @@
       </c>
       <c r="W79" s="23"/>
       <c r="X79" s="148" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="Y79" s="151" t="s">
         <v>86</v>
@@ -26127,7 +26129,7 @@
       <c r="AA79" s="43"/>
       <c r="AB79" s="43"/>
       <c r="AC79" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD79" s="23"/>
       <c r="AE79" s="23"/>
@@ -26135,7 +26137,7 @@
       <c r="AG79" s="23"/>
       <c r="AH79" s="23"/>
       <c r="AI79" s="134" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="80" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -26152,16 +26154,16 @@
         <v>341</v>
       </c>
       <c r="E80" s="129" t="s">
+        <v>886</v>
+      </c>
+      <c r="F80" s="129" t="s">
         <v>887</v>
-      </c>
-      <c r="F80" s="129" t="s">
-        <v>888</v>
       </c>
       <c r="G80" s="46" t="s">
         <v>351</v>
       </c>
       <c r="H80" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I80" s="43" t="s">
         <v>343</v>
@@ -26179,11 +26181,11 @@
         <v>354</v>
       </c>
       <c r="N80" s="129" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="O80" s="129"/>
       <c r="P80" s="43" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="Q80" s="43"/>
       <c r="R80" s="43" t="s">
@@ -26203,7 +26205,7 @@
       </c>
       <c r="W80" s="23"/>
       <c r="X80" s="148" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="Y80" s="151" t="s">
         <v>86</v>
@@ -26214,7 +26216,7 @@
       <c r="AA80" s="43"/>
       <c r="AB80" s="43"/>
       <c r="AC80" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD80" s="23"/>
       <c r="AE80" s="23"/>
@@ -26222,7 +26224,7 @@
       <c r="AG80" s="23"/>
       <c r="AH80" s="23"/>
       <c r="AI80" s="134" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="81" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -26239,16 +26241,16 @@
         <v>341</v>
       </c>
       <c r="E81" s="129" t="s">
+        <v>886</v>
+      </c>
+      <c r="F81" s="129" t="s">
         <v>887</v>
-      </c>
-      <c r="F81" s="129" t="s">
-        <v>888</v>
       </c>
       <c r="G81" s="46" t="s">
         <v>351</v>
       </c>
       <c r="H81" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I81" s="43" t="s">
         <v>343</v>
@@ -26266,11 +26268,11 @@
         <v>357</v>
       </c>
       <c r="N81" s="129" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="O81" s="139"/>
       <c r="P81" s="48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="Q81" s="48"/>
       <c r="R81" s="43" t="s">
@@ -26290,7 +26292,7 @@
       </c>
       <c r="W81" s="23"/>
       <c r="X81" s="148" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="Y81" s="151" t="s">
         <v>86</v>
@@ -26301,7 +26303,7 @@
       <c r="AA81" s="43"/>
       <c r="AB81" s="23"/>
       <c r="AC81" s="23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AD81" s="23" t="s">
         <v>359</v>
@@ -26311,7 +26313,7 @@
       <c r="AG81" s="23"/>
       <c r="AH81" s="43"/>
       <c r="AI81" s="134" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="82" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -26328,16 +26330,16 @@
         <v>360</v>
       </c>
       <c r="E82" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F82" s="141" t="s">
         <v>904</v>
-      </c>
-      <c r="F82" s="141" t="s">
-        <v>905</v>
       </c>
       <c r="G82" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H82" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I82" s="43" t="s">
         <v>209</v>
@@ -26362,7 +26364,7 @@
         <v>364</v>
       </c>
       <c r="Q82" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R82" s="43" t="s">
         <v>62</v>
@@ -26390,7 +26392,7 @@
       <c r="AA82" s="43"/>
       <c r="AB82" s="23"/>
       <c r="AC82" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD82" s="23"/>
       <c r="AE82" s="23"/>
@@ -26413,16 +26415,16 @@
         <v>360</v>
       </c>
       <c r="E83" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F83" s="141" t="s">
         <v>904</v>
-      </c>
-      <c r="F83" s="141" t="s">
-        <v>905</v>
       </c>
       <c r="G83" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H83" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I83" s="43" t="s">
         <v>209</v>
@@ -26444,10 +26446,10 @@
       </c>
       <c r="O83" s="48"/>
       <c r="P83" s="48" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Q83" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R83" s="43" t="s">
         <v>62</v>
@@ -26475,7 +26477,7 @@
       <c r="AA83" s="43"/>
       <c r="AB83" s="23"/>
       <c r="AC83" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD83" s="23"/>
       <c r="AE83" s="23"/>
@@ -26498,10 +26500,10 @@
         <v>360</v>
       </c>
       <c r="E84" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F84" s="141" t="s">
         <v>904</v>
-      </c>
-      <c r="F84" s="141" t="s">
-        <v>905</v>
       </c>
       <c r="G84" s="46" t="s">
         <v>34</v>
@@ -26527,10 +26529,10 @@
       </c>
       <c r="O84" s="43"/>
       <c r="P84" s="41" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="Q84" s="41" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R84" s="43" t="s">
         <v>62</v>
@@ -26558,7 +26560,7 @@
       <c r="AA84" s="43"/>
       <c r="AB84" s="23"/>
       <c r="AC84" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD84" s="23"/>
       <c r="AE84" s="23"/>
@@ -26581,10 +26583,10 @@
         <v>360</v>
       </c>
       <c r="E85" s="41" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F85" s="141" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G85" s="46" t="s">
         <v>34</v>
@@ -26613,7 +26615,7 @@
         <v>373</v>
       </c>
       <c r="Q85" s="48" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R85" s="43" t="s">
         <v>62</v>
@@ -26641,7 +26643,7 @@
       <c r="AA85" s="43"/>
       <c r="AB85" s="23"/>
       <c r="AC85" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD85" s="23"/>
       <c r="AE85" s="23"/>
@@ -26664,10 +26666,10 @@
         <v>360</v>
       </c>
       <c r="E86" s="41" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F86" s="141" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G86" s="46" t="s">
         <v>34</v>
@@ -26680,7 +26682,7 @@
         <v>37</v>
       </c>
       <c r="K86" s="43" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="L86" s="43" t="s">
         <v>125</v>
@@ -26693,10 +26695,10 @@
       </c>
       <c r="O86" s="56"/>
       <c r="P86" s="56" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="Q86" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R86" s="43" t="s">
         <v>75</v>
@@ -26724,7 +26726,7 @@
       <c r="AA86" s="43"/>
       <c r="AB86" s="23"/>
       <c r="AC86" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD86" s="23"/>
       <c r="AE86" s="23"/>
@@ -26749,13 +26751,13 @@
         <v>360</v>
       </c>
       <c r="E87" s="41" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F87" s="141" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G87" s="46" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H87" s="46"/>
       <c r="I87" s="43" t="s">
@@ -26763,30 +26765,30 @@
       </c>
       <c r="J87" s="43"/>
       <c r="K87" s="43" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L87" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M87" s="78" t="s">
+        <v>915</v>
+      </c>
+      <c r="N87" s="110" t="s">
         <v>916</v>
-      </c>
-      <c r="N87" s="110" t="s">
-        <v>917</v>
       </c>
       <c r="O87" s="111"/>
       <c r="P87" s="111" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="Q87" s="56"/>
       <c r="R87" s="43" t="s">
         <v>75</v>
       </c>
       <c r="S87" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="T87" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="U87" s="43" t="s">
         <v>45</v>
@@ -26796,16 +26798,16 @@
       </c>
       <c r="W87" s="90"/>
       <c r="X87" s="119" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="Y87" s="119"/>
       <c r="Z87" s="23" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AA87" s="23"/>
       <c r="AB87" s="23"/>
       <c r="AC87" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD87" s="23"/>
       <c r="AE87" s="23"/>
@@ -26828,13 +26830,13 @@
         <v>360</v>
       </c>
       <c r="E88" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F88" s="141" t="s">
         <v>904</v>
       </c>
-      <c r="F88" s="141" t="s">
-        <v>905</v>
-      </c>
       <c r="G88" s="46" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H88" s="46"/>
       <c r="I88" s="43" t="s">
@@ -26850,17 +26852,17 @@
         <v>125</v>
       </c>
       <c r="M88" s="78" t="s">
+        <v>920</v>
+      </c>
+      <c r="N88" s="112" t="s">
         <v>921</v>
-      </c>
-      <c r="N88" s="112" t="s">
-        <v>922</v>
       </c>
       <c r="O88" s="113"/>
       <c r="P88" s="113" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Q88" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R88" s="43" t="s">
         <v>62</v>
@@ -26890,7 +26892,7 @@
       <c r="AA88" s="23"/>
       <c r="AB88" s="23"/>
       <c r="AC88" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD88" s="23"/>
       <c r="AE88" s="23"/>
@@ -26913,13 +26915,13 @@
         <v>360</v>
       </c>
       <c r="E89" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F89" s="141" t="s">
         <v>904</v>
       </c>
-      <c r="F89" s="141" t="s">
-        <v>905</v>
-      </c>
       <c r="G89" s="46" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H89" s="46"/>
       <c r="I89" s="43" t="s">
@@ -26933,17 +26935,17 @@
         <v>125</v>
       </c>
       <c r="M89" s="78" t="s">
+        <v>923</v>
+      </c>
+      <c r="N89" s="112" t="s">
         <v>924</v>
-      </c>
-      <c r="N89" s="112" t="s">
-        <v>925</v>
       </c>
       <c r="O89" s="113"/>
       <c r="P89" s="113" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="Q89" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R89" s="43" t="s">
         <v>62</v>
@@ -26973,7 +26975,7 @@
       <c r="AA89" s="23"/>
       <c r="AB89" s="23"/>
       <c r="AC89" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD89" s="23"/>
       <c r="AE89" s="23"/>
@@ -26996,13 +26998,13 @@
         <v>360</v>
       </c>
       <c r="E90" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="F90" s="141" t="s">
         <v>904</v>
       </c>
-      <c r="F90" s="141" t="s">
-        <v>905</v>
-      </c>
       <c r="G90" s="89" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H90" s="46"/>
       <c r="I90" s="43" t="s">
@@ -27018,14 +27020,14 @@
         <v>39</v>
       </c>
       <c r="M90" s="78" t="s">
+        <v>926</v>
+      </c>
+      <c r="N90" s="112" t="s">
         <v>927</v>
-      </c>
-      <c r="N90" s="112" t="s">
-        <v>928</v>
       </c>
       <c r="O90" s="113"/>
       <c r="P90" s="113" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q90" s="56" t="s">
         <v>37</v>
@@ -27058,7 +27060,7 @@
       <c r="AA90" s="23"/>
       <c r="AB90" s="23"/>
       <c r="AC90" s="23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AD90" s="23"/>
       <c r="AE90" s="23"/>
@@ -27072,7 +27074,7 @@
         <v>206</v>
       </c>
       <c r="B91" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>31</v>
@@ -27125,7 +27127,7 @@
       <c r="AA91" s="6"/>
       <c r="AB91" s="6"/>
       <c r="AC91" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AD91" s="6" t="s">
         <v>271</v>
@@ -27150,10 +27152,10 @@
         <v>383</v>
       </c>
       <c r="E92" s="43" t="s">
+        <v>929</v>
+      </c>
+      <c r="F92" s="43" t="s">
         <v>930</v>
-      </c>
-      <c r="F92" s="43" t="s">
-        <v>931</v>
       </c>
       <c r="G92" s="46" t="s">
         <v>34</v>
@@ -27175,11 +27177,11 @@
         <v>386</v>
       </c>
       <c r="N92" s="115" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O92" s="115"/>
       <c r="P92" s="115" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="Q92" s="43"/>
       <c r="R92" s="43" t="s">
@@ -27202,7 +27204,7 @@
       <c r="AA92" s="43"/>
       <c r="AB92" s="23"/>
       <c r="AC92" s="23" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AD92" s="23"/>
       <c r="AE92" s="23"/>
@@ -27225,10 +27227,10 @@
         <v>383</v>
       </c>
       <c r="E93" s="43" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F93" s="43" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G93" s="46" t="s">
         <v>34</v>
@@ -27250,7 +27252,7 @@
         <v>389</v>
       </c>
       <c r="N93" s="43" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O93" s="43"/>
       <c r="P93" s="43"/>
@@ -27275,7 +27277,7 @@
       <c r="AA93" s="43"/>
       <c r="AB93" s="23"/>
       <c r="AC93" s="23" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AD93" s="23"/>
       <c r="AE93" s="23"/>
@@ -27298,10 +27300,10 @@
         <v>383</v>
       </c>
       <c r="E94" s="43" t="s">
+        <v>935</v>
+      </c>
+      <c r="F94" s="43" t="s">
         <v>936</v>
-      </c>
-      <c r="F94" s="43" t="s">
-        <v>937</v>
       </c>
       <c r="G94" s="46" t="s">
         <v>34</v>
@@ -27330,7 +27332,7 @@
         <v>392</v>
       </c>
       <c r="Q94" s="43" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R94" s="43" t="s">
         <v>62</v>
@@ -27356,7 +27358,7 @@
       <c r="AA94" s="43"/>
       <c r="AB94" s="23"/>
       <c r="AC94" s="23" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AD94" s="23"/>
       <c r="AE94" s="23"/>
@@ -27376,7 +27378,7 @@
         <v>382</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>427</v>
@@ -27423,7 +27425,7 @@
         <v>225</v>
       </c>
       <c r="B96" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C96" s="45" t="s">
         <v>163</v>
@@ -27432,10 +27434,10 @@
         <v>393</v>
       </c>
       <c r="E96" s="38" t="s">
+        <v>938</v>
+      </c>
+      <c r="F96" s="143" t="s">
         <v>939</v>
-      </c>
-      <c r="F96" s="143" t="s">
-        <v>940</v>
       </c>
       <c r="G96" s="46" t="s">
         <v>34</v>
@@ -27462,7 +27464,7 @@
         <v>398</v>
       </c>
       <c r="Q96" s="43" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="R96" s="43" t="s">
         <v>399</v>
@@ -27508,7 +27510,7 @@
         <v>111</v>
       </c>
       <c r="B97" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C97" s="45" t="s">
         <v>163</v>
@@ -27544,7 +27546,7 @@
       </c>
       <c r="O97" s="43"/>
       <c r="P97" s="57" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="Q97" s="57"/>
       <c r="R97" s="43" t="s">
@@ -27640,7 +27642,7 @@
       <c r="AA98" s="43"/>
       <c r="AB98" s="23"/>
       <c r="AC98" s="23" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AD98" s="23" t="s">
         <v>415</v>
@@ -27665,10 +27667,10 @@
         <v>416</v>
       </c>
       <c r="E99" s="43" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F99" s="43" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G99" s="46" t="s">
         <v>34</v>
@@ -27715,7 +27717,7 @@
       <c r="AA99" s="43"/>
       <c r="AB99" s="23"/>
       <c r="AC99" s="23" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AD99" s="23" t="s">
         <v>346</v>
@@ -27740,16 +27742,16 @@
         <v>420</v>
       </c>
       <c r="E100" s="43" t="s">
+        <v>943</v>
+      </c>
+      <c r="F100" s="43" t="s">
         <v>944</v>
-      </c>
-      <c r="F100" s="43" t="s">
-        <v>945</v>
       </c>
       <c r="G100" s="46" t="s">
         <v>351</v>
       </c>
       <c r="H100" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I100" s="43" t="s">
         <v>420</v>
@@ -27758,18 +27760,18 @@
         <v>37</v>
       </c>
       <c r="K100" s="43" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L100" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M100" s="76" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="N100" s="43"/>
       <c r="O100" s="43"/>
       <c r="P100" s="50" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="Q100" s="50"/>
       <c r="R100" s="43"/>
@@ -27782,11 +27784,11 @@
       <c r="Y100" s="119"/>
       <c r="Z100" s="43"/>
       <c r="AA100" s="53" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="AB100" s="23"/>
       <c r="AC100" s="23" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AD100" s="23"/>
       <c r="AE100" s="23"/>
@@ -27809,16 +27811,16 @@
         <v>420</v>
       </c>
       <c r="E101" s="129" t="s">
+        <v>949</v>
+      </c>
+      <c r="F101" s="129" t="s">
         <v>950</v>
-      </c>
-      <c r="F101" s="129" t="s">
-        <v>951</v>
       </c>
       <c r="G101" s="46" t="s">
         <v>351</v>
       </c>
       <c r="H101" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I101" s="43" t="s">
         <v>420</v>
@@ -27833,13 +27835,13 @@
         <v>39</v>
       </c>
       <c r="M101" s="76" t="s">
+        <v>951</v>
+      </c>
+      <c r="N101" s="129" t="s">
         <v>952</v>
       </c>
-      <c r="N101" s="129" t="s">
+      <c r="O101" s="129" t="s">
         <v>953</v>
-      </c>
-      <c r="O101" s="129" t="s">
-        <v>954</v>
       </c>
       <c r="P101" s="50" t="s">
         <v>425</v>
@@ -27862,10 +27864,10 @@
       </c>
       <c r="W101" s="23"/>
       <c r="X101" s="148" t="s">
+        <v>954</v>
+      </c>
+      <c r="Y101" s="151" t="s">
         <v>955</v>
-      </c>
-      <c r="Y101" s="151" t="s">
-        <v>956</v>
       </c>
       <c r="Z101" s="43" t="s">
         <v>49</v>
@@ -27873,7 +27875,7 @@
       <c r="AA101" s="43"/>
       <c r="AB101" s="23"/>
       <c r="AC101" s="23" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AD101" s="23"/>
       <c r="AE101" s="23"/>
@@ -27881,7 +27883,7 @@
       <c r="AG101" s="23"/>
       <c r="AH101" s="43"/>
       <c r="AI101" s="134" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="102" spans="1:35" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -27948,7 +27950,7 @@
         <v>225</v>
       </c>
       <c r="B103" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C103" s="45" t="s">
         <v>31</v>
@@ -27979,7 +27981,7 @@
         <v>37</v>
       </c>
       <c r="M103" s="76" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="N103" s="43" t="s">
         <v>442</v>
@@ -28013,7 +28015,7 @@
       <c r="AA103" s="43"/>
       <c r="AB103" s="6"/>
       <c r="AC103" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AD103" s="6" t="s">
         <v>445</v>
@@ -28029,7 +28031,7 @@
         <v>225</v>
       </c>
       <c r="B104" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C104" s="45" t="s">
         <v>31</v>
@@ -28060,7 +28062,7 @@
         <v>37</v>
       </c>
       <c r="M104" s="76" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="N104" s="43" t="s">
         <v>442</v>
@@ -28094,7 +28096,7 @@
       <c r="AA104" s="43"/>
       <c r="AB104" s="6"/>
       <c r="AC104" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AD104" s="6" t="s">
         <v>445</v>
@@ -28219,16 +28221,16 @@
         <v>455</v>
       </c>
       <c r="E107" s="129" t="s">
+        <v>959</v>
+      </c>
+      <c r="F107" s="129" t="s">
         <v>960</v>
-      </c>
-      <c r="F107" s="129" t="s">
-        <v>961</v>
       </c>
       <c r="G107" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H107" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I107" s="43" t="s">
         <v>167</v>
@@ -28246,10 +28248,10 @@
         <v>278</v>
       </c>
       <c r="N107" s="129" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="O107" s="129" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P107" s="43" t="s">
         <v>459</v>
@@ -28272,7 +28274,7 @@
       </c>
       <c r="W107" s="23"/>
       <c r="X107" s="148" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Y107" s="151" t="s">
         <v>86</v>
@@ -28283,7 +28285,7 @@
       <c r="AA107" s="43"/>
       <c r="AB107" s="23"/>
       <c r="AC107" s="23" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AD107" s="23" t="s">
         <v>120</v>
@@ -28295,7 +28297,7 @@
         <v>460</v>
       </c>
       <c r="AI107" s="134" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="108" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -28312,16 +28314,16 @@
         <v>455</v>
       </c>
       <c r="E108" s="129" t="s">
+        <v>959</v>
+      </c>
+      <c r="F108" s="129" t="s">
         <v>960</v>
-      </c>
-      <c r="F108" s="129" t="s">
-        <v>961</v>
       </c>
       <c r="G108" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H108" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I108" s="43" t="s">
         <v>167</v>
@@ -28339,10 +28341,10 @@
         <v>461</v>
       </c>
       <c r="N108" s="129" t="s">
+        <v>964</v>
+      </c>
+      <c r="O108" s="129" t="s">
         <v>965</v>
-      </c>
-      <c r="O108" s="129" t="s">
-        <v>966</v>
       </c>
       <c r="P108" s="43" t="s">
         <v>464</v>
@@ -28367,10 +28369,10 @@
         <v>47</v>
       </c>
       <c r="X108" s="148" t="s">
+        <v>966</v>
+      </c>
+      <c r="Y108" s="151" t="s">
         <v>967</v>
-      </c>
-      <c r="Y108" s="151" t="s">
-        <v>968</v>
       </c>
       <c r="Z108" s="43" t="s">
         <v>49</v>
@@ -28378,7 +28380,7 @@
       <c r="AA108" s="43"/>
       <c r="AB108" s="23"/>
       <c r="AC108" s="23" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AD108" s="23" t="s">
         <v>120</v>
@@ -28392,7 +28394,7 @@
         <v>460</v>
       </c>
       <c r="AI108" s="134" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="109" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -28409,16 +28411,16 @@
         <v>455</v>
       </c>
       <c r="E109" s="129" t="s">
+        <v>959</v>
+      </c>
+      <c r="F109" s="129" t="s">
         <v>960</v>
-      </c>
-      <c r="F109" s="129" t="s">
-        <v>961</v>
       </c>
       <c r="G109" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H109" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I109" s="43" t="s">
         <v>167</v>
@@ -28433,10 +28435,10 @@
         <v>125</v>
       </c>
       <c r="M109" s="76" t="s">
+        <v>969</v>
+      </c>
+      <c r="N109" s="129" t="s">
         <v>970</v>
-      </c>
-      <c r="N109" s="129" t="s">
-        <v>971</v>
       </c>
       <c r="O109" s="129"/>
       <c r="P109" s="43" t="s">
@@ -28469,7 +28471,7 @@
       <c r="AA109" s="43"/>
       <c r="AB109" s="23"/>
       <c r="AC109" s="23" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AD109" s="23"/>
       <c r="AE109" s="23"/>
@@ -28479,7 +28481,7 @@
         <v>460</v>
       </c>
       <c r="AI109" s="134" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="110" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -28496,16 +28498,16 @@
         <v>455</v>
       </c>
       <c r="E110" s="141" t="s">
+        <v>972</v>
+      </c>
+      <c r="F110" s="141" t="s">
         <v>973</v>
-      </c>
-      <c r="F110" s="141" t="s">
-        <v>974</v>
       </c>
       <c r="G110" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H110" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I110" s="43" t="s">
         <v>167</v>
@@ -28514,7 +28516,7 @@
         <v>37</v>
       </c>
       <c r="K110" s="106" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="L110" s="43" t="s">
         <v>125</v>
@@ -28538,7 +28540,7 @@
       <c r="AA110" s="43"/>
       <c r="AB110" s="23"/>
       <c r="AC110" s="23" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AD110" s="23"/>
       <c r="AE110" s="23"/>
@@ -28597,7 +28599,7 @@
       <c r="AA111" s="6"/>
       <c r="AB111" s="6"/>
       <c r="AC111" s="107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AD111" s="6"/>
       <c r="AE111" s="6"/>
@@ -28662,7 +28664,7 @@
       <c r="AA112" s="6"/>
       <c r="AB112" s="6"/>
       <c r="AC112" s="107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AD112" s="6"/>
       <c r="AE112" s="6"/>
@@ -28727,7 +28729,7 @@
       <c r="AA113" s="6"/>
       <c r="AB113" s="6"/>
       <c r="AC113" s="107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AD113" s="6"/>
       <c r="AE113" s="6"/>
@@ -28790,7 +28792,7 @@
       <c r="AA114" s="6"/>
       <c r="AB114" s="6"/>
       <c r="AC114" s="107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AD114" s="6"/>
       <c r="AE114" s="6"/>
@@ -28857,7 +28859,7 @@
       <c r="AA115" s="6"/>
       <c r="AB115" s="6"/>
       <c r="AC115" s="107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AD115" s="6" t="s">
         <v>271</v>
@@ -28873,7 +28875,7 @@
         <v>111</v>
       </c>
       <c r="B116" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C116" s="45" t="s">
         <v>273</v>
@@ -28882,16 +28884,16 @@
         <v>479</v>
       </c>
       <c r="E116" s="128" t="s">
+        <v>976</v>
+      </c>
+      <c r="F116" s="128" t="s">
         <v>977</v>
-      </c>
-      <c r="F116" s="128" t="s">
-        <v>978</v>
       </c>
       <c r="G116" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H116" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I116" s="43" t="s">
         <v>480</v>
@@ -28906,19 +28908,19 @@
         <v>39</v>
       </c>
       <c r="M116" s="76" t="s">
+        <v>978</v>
+      </c>
+      <c r="N116" s="129" t="s">
         <v>979</v>
       </c>
-      <c r="N116" s="129" t="s">
+      <c r="O116" s="129" t="s">
         <v>980</v>
       </c>
-      <c r="O116" s="129" t="s">
+      <c r="P116" s="43" t="s">
         <v>981</v>
       </c>
-      <c r="P116" s="43" t="s">
-        <v>982</v>
-      </c>
       <c r="Q116" s="50" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R116" s="43" t="s">
         <v>202</v>
@@ -28939,16 +28941,16 @@
         <v>47</v>
       </c>
       <c r="X116" s="148" t="s">
+        <v>982</v>
+      </c>
+      <c r="Y116" s="151" t="s">
         <v>983</v>
-      </c>
-      <c r="Y116" s="151" t="s">
-        <v>984</v>
       </c>
       <c r="Z116" s="43"/>
       <c r="AA116" s="43"/>
       <c r="AB116" s="6"/>
       <c r="AC116" s="6" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AD116" s="6"/>
       <c r="AE116" s="6"/>
@@ -28956,7 +28958,7 @@
       <c r="AG116" s="6"/>
       <c r="AH116" s="43"/>
       <c r="AI116" s="134" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="117" spans="1:35" ht="90.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -29015,7 +29017,7 @@
         <v>206</v>
       </c>
       <c r="B118" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C118" s="45" t="s">
         <v>53</v>
@@ -29024,16 +29026,16 @@
         <v>486</v>
       </c>
       <c r="E118" s="129" t="s">
+        <v>986</v>
+      </c>
+      <c r="F118" s="129" t="s">
         <v>987</v>
-      </c>
-      <c r="F118" s="129" t="s">
-        <v>988</v>
       </c>
       <c r="G118" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H118" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I118" s="43" t="s">
         <v>171</v>
@@ -29046,16 +29048,16 @@
         <v>39</v>
       </c>
       <c r="M118" s="76" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N118" s="133" t="s">
+        <v>988</v>
+      </c>
+      <c r="O118" s="133" t="s">
         <v>989</v>
       </c>
-      <c r="O118" s="133" t="s">
+      <c r="P118" s="43" t="s">
         <v>990</v>
-      </c>
-      <c r="P118" s="43" t="s">
-        <v>991</v>
       </c>
       <c r="Q118" s="43"/>
       <c r="R118" s="6"/>
@@ -29065,7 +29067,7 @@
       <c r="V118" s="6"/>
       <c r="W118" s="7"/>
       <c r="X118" s="152" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="Y118" s="151" t="s">
         <v>86</v>
@@ -29074,7 +29076,7 @@
       <c r="AA118" s="6"/>
       <c r="AB118" s="6"/>
       <c r="AC118" s="6" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AD118" s="6"/>
       <c r="AE118" s="6"/>
@@ -29082,7 +29084,7 @@
       <c r="AG118" s="6"/>
       <c r="AH118" s="6"/>
       <c r="AI118" s="134" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="119" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29090,7 +29092,7 @@
         <v>206</v>
       </c>
       <c r="B119" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C119" s="45" t="s">
         <v>53</v>
@@ -29099,38 +29101,38 @@
         <v>486</v>
       </c>
       <c r="E119" s="129" t="s">
+        <v>986</v>
+      </c>
+      <c r="F119" s="129" t="s">
         <v>987</v>
-      </c>
-      <c r="F119" s="129" t="s">
-        <v>988</v>
       </c>
       <c r="G119" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H119" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>171</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119" s="43" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L119" s="43" t="s">
         <v>39</v>
       </c>
       <c r="M119" s="76" t="s">
+        <v>994</v>
+      </c>
+      <c r="N119" s="133" t="s">
         <v>995</v>
       </c>
-      <c r="N119" s="133" t="s">
+      <c r="O119" s="140" t="s">
         <v>996</v>
       </c>
-      <c r="O119" s="140" t="s">
+      <c r="P119" s="7" t="s">
         <v>997</v>
-      </c>
-      <c r="P119" s="7" t="s">
-        <v>998</v>
       </c>
       <c r="Q119" s="7"/>
       <c r="R119" s="6"/>
@@ -29140,10 +29142,10 @@
       <c r="V119" s="6"/>
       <c r="W119" s="7"/>
       <c r="X119" s="152" t="s">
+        <v>998</v>
+      </c>
+      <c r="Y119" s="151" t="s">
         <v>999</v>
-      </c>
-      <c r="Y119" s="151" t="s">
-        <v>1000</v>
       </c>
       <c r="Z119" s="6" t="s">
         <v>203</v>
@@ -29151,7 +29153,7 @@
       <c r="AA119" s="6"/>
       <c r="AB119" s="6"/>
       <c r="AC119" s="6" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AD119" s="6"/>
       <c r="AE119" s="6"/>
@@ -29159,7 +29161,7 @@
       <c r="AG119" s="6"/>
       <c r="AH119" s="6"/>
       <c r="AI119" s="134" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="120" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29167,7 +29169,7 @@
         <v>206</v>
       </c>
       <c r="B120" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C120" s="45" t="s">
         <v>53</v>
@@ -29176,16 +29178,16 @@
         <v>486</v>
       </c>
       <c r="E120" s="129" t="s">
+        <v>986</v>
+      </c>
+      <c r="F120" s="129" t="s">
         <v>987</v>
-      </c>
-      <c r="F120" s="129" t="s">
-        <v>988</v>
       </c>
       <c r="G120" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H120" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I120" s="43" t="s">
         <v>171</v>
@@ -29198,16 +29200,16 @@
         <v>39</v>
       </c>
       <c r="M120" s="76" t="s">
+        <v>1001</v>
+      </c>
+      <c r="N120" s="129" t="s">
+        <v>738</v>
+      </c>
+      <c r="O120" s="129" t="s">
         <v>1002</v>
       </c>
-      <c r="N120" s="129" t="s">
-        <v>739</v>
-      </c>
-      <c r="O120" s="129" t="s">
+      <c r="P120" s="43" t="s">
         <v>1003</v>
-      </c>
-      <c r="P120" s="43" t="s">
-        <v>1004</v>
       </c>
       <c r="Q120" s="43"/>
       <c r="R120" s="43" t="s">
@@ -29223,7 +29225,7 @@
       <c r="V120" s="43"/>
       <c r="W120" s="6"/>
       <c r="X120" s="152" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Y120" s="151" t="s">
         <v>86</v>
@@ -29232,7 +29234,7 @@
       <c r="AA120" s="43"/>
       <c r="AB120" s="6"/>
       <c r="AC120" s="6" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AD120" s="6"/>
       <c r="AE120" s="6"/>
@@ -29240,7 +29242,7 @@
       <c r="AG120" s="6"/>
       <c r="AH120" s="43"/>
       <c r="AI120" s="134" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="121" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29248,7 +29250,7 @@
         <v>107</v>
       </c>
       <c r="B121" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C121" s="45" t="s">
         <v>273</v>
@@ -29257,16 +29259,16 @@
         <v>491</v>
       </c>
       <c r="E121" s="131" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F121" s="131" t="s">
         <v>1007</v>
-      </c>
-      <c r="F121" s="131" t="s">
-        <v>1008</v>
       </c>
       <c r="G121" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H121" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I121" s="43" t="s">
         <v>480</v>
@@ -29282,16 +29284,16 @@
         <v>493</v>
       </c>
       <c r="N121" s="129" t="s">
+        <v>1008</v>
+      </c>
+      <c r="O121" s="129" t="s">
         <v>1009</v>
       </c>
-      <c r="O121" s="129" t="s">
+      <c r="P121" s="43" t="s">
         <v>1010</v>
       </c>
-      <c r="P121" s="43" t="s">
+      <c r="Q121" s="43" t="s">
         <v>1011</v>
-      </c>
-      <c r="Q121" s="43" t="s">
-        <v>1012</v>
       </c>
       <c r="R121" s="43" t="s">
         <v>329</v>
@@ -29306,16 +29308,16 @@
       <c r="V121" s="43"/>
       <c r="W121" s="6"/>
       <c r="X121" s="148" t="s">
+        <v>1012</v>
+      </c>
+      <c r="Y121" s="151" t="s">
         <v>1013</v>
-      </c>
-      <c r="Y121" s="151" t="s">
-        <v>1014</v>
       </c>
       <c r="Z121" s="43"/>
       <c r="AA121" s="43"/>
       <c r="AB121" s="6"/>
       <c r="AC121" s="6" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AD121" s="6"/>
       <c r="AE121" s="6"/>
@@ -29323,7 +29325,7 @@
       <c r="AG121" s="6"/>
       <c r="AH121" s="43"/>
       <c r="AI121" s="134" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="122" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29331,7 +29333,7 @@
         <v>107</v>
       </c>
       <c r="B122" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C122" s="45" t="s">
         <v>273</v>
@@ -29340,16 +29342,16 @@
         <v>491</v>
       </c>
       <c r="E122" s="131" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F122" s="131" t="s">
         <v>1007</v>
-      </c>
-      <c r="F122" s="131" t="s">
-        <v>1008</v>
       </c>
       <c r="G122" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H122" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I122" s="43" t="s">
         <v>480</v>
@@ -29365,14 +29367,14 @@
         <v>494</v>
       </c>
       <c r="N122" s="129" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="O122" s="129"/>
       <c r="P122" s="43" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q122" s="43" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="R122" s="43" t="s">
         <v>329</v>
@@ -29391,7 +29393,7 @@
       </c>
       <c r="W122" s="6"/>
       <c r="X122" s="152" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Y122" s="151" t="s">
         <v>86</v>
@@ -29402,7 +29404,7 @@
       <c r="AA122" s="43"/>
       <c r="AB122" s="6"/>
       <c r="AC122" s="6" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AD122" s="6"/>
       <c r="AE122" s="6"/>
@@ -29410,7 +29412,7 @@
       <c r="AG122" s="6"/>
       <c r="AH122" s="43"/>
       <c r="AI122" s="134" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="123" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29418,7 +29420,7 @@
         <v>107</v>
       </c>
       <c r="B123" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C123" s="45" t="s">
         <v>273</v>
@@ -29427,16 +29429,16 @@
         <v>491</v>
       </c>
       <c r="E123" s="131" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F123" s="131" t="s">
         <v>1007</v>
-      </c>
-      <c r="F123" s="131" t="s">
-        <v>1008</v>
       </c>
       <c r="G123" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H123" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I123" s="43" t="s">
         <v>480</v>
@@ -29452,16 +29454,16 @@
         <v>283</v>
       </c>
       <c r="N123" s="129" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O123" s="129" t="s">
         <v>1020</v>
       </c>
-      <c r="O123" s="129" t="s">
+      <c r="P123" s="43" t="s">
         <v>1021</v>
       </c>
-      <c r="P123" s="43" t="s">
-        <v>1022</v>
-      </c>
       <c r="Q123" s="43" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="R123" s="43" t="s">
         <v>75</v>
@@ -29480,16 +29482,16 @@
       </c>
       <c r="W123" s="6"/>
       <c r="X123" s="148" t="s">
+        <v>586</v>
+      </c>
+      <c r="Y123" s="151" t="s">
         <v>587</v>
-      </c>
-      <c r="Y123" s="151" t="s">
-        <v>588</v>
       </c>
       <c r="Z123" s="43"/>
       <c r="AA123" s="43"/>
       <c r="AB123" s="6"/>
       <c r="AC123" s="145" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AD123" s="6"/>
       <c r="AE123" s="6"/>
@@ -29497,7 +29499,7 @@
       <c r="AG123" s="6"/>
       <c r="AH123" s="43"/>
       <c r="AI123" s="134" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="124" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
@@ -29514,16 +29516,16 @@
         <v>496</v>
       </c>
       <c r="E124" s="129" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F124" s="129" t="s">
         <v>1025</v>
-      </c>
-      <c r="F124" s="129" t="s">
-        <v>1026</v>
       </c>
       <c r="G124" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H124" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I124" s="43" t="s">
         <v>498</v>
@@ -29538,10 +29540,10 @@
         <v>125</v>
       </c>
       <c r="M124" s="76" t="s">
+        <v>1026</v>
+      </c>
+      <c r="N124" s="129" t="s">
         <v>1027</v>
-      </c>
-      <c r="N124" s="129" t="s">
-        <v>1028</v>
       </c>
       <c r="O124" s="139"/>
       <c r="P124" s="48" t="s">
@@ -29565,7 +29567,7 @@
       </c>
       <c r="W124" s="23"/>
       <c r="X124" s="149" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Y124" s="151" t="s">
         <v>86</v>
@@ -29576,7 +29578,7 @@
       <c r="AA124" s="43"/>
       <c r="AB124" s="23"/>
       <c r="AC124" s="23" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AD124" s="23" t="s">
         <v>505</v>
@@ -29586,7 +29588,7 @@
       <c r="AG124" s="23"/>
       <c r="AH124" s="43"/>
       <c r="AI124" s="134" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="125" spans="1:35" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
@@ -29603,16 +29605,16 @@
         <v>496</v>
       </c>
       <c r="E125" s="43" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F125" s="43" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G125" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H125" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I125" s="43" t="s">
         <v>498</v>
@@ -29625,7 +29627,7 @@
         <v>125</v>
       </c>
       <c r="M125" s="78" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="N125" s="55" t="s">
         <v>507</v>
@@ -29657,7 +29659,7 @@
       <c r="AA125" s="43"/>
       <c r="AB125" s="23"/>
       <c r="AC125" s="23" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AD125" s="23"/>
       <c r="AE125" s="23"/>
@@ -29680,16 +29682,16 @@
         <v>496</v>
       </c>
       <c r="E126" s="43" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F126" s="43" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G126" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H126" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I126" s="43" t="s">
         <v>498</v>
@@ -29738,7 +29740,7 @@
       <c r="AA126" s="43"/>
       <c r="AB126" s="23"/>
       <c r="AC126" s="23" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AD126" s="23" t="s">
         <v>505</v>
@@ -29765,16 +29767,16 @@
         <v>496</v>
       </c>
       <c r="E127" s="43" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F127" s="43" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G127" s="46" t="s">
         <v>34</v>
       </c>
       <c r="H127" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I127" s="43" t="s">
         <v>498</v>
@@ -29805,7 +29807,7 @@
       <c r="S127" s="43"/>
       <c r="T127" s="43"/>
       <c r="U127" s="43" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="V127" s="43" t="s">
         <v>77</v>
@@ -29821,7 +29823,7 @@
       <c r="AA127" s="43"/>
       <c r="AB127" s="23"/>
       <c r="AC127" s="23" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AD127" s="23" t="s">
         <v>505</v>
@@ -29846,10 +29848,10 @@
         <v>522</v>
       </c>
       <c r="E128" s="51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F128" s="51" t="s">
         <v>1035</v>
-      </c>
-      <c r="F128" s="51" t="s">
-        <v>1036</v>
       </c>
       <c r="G128" s="46" t="s">
         <v>34</v>
@@ -29869,14 +29871,14 @@
         <v>524</v>
       </c>
       <c r="N128" s="43" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="O128" s="67"/>
       <c r="P128" s="40" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q128" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R128" s="48" t="s">
         <v>62</v>
@@ -29904,7 +29906,7 @@
       <c r="AA128" s="43"/>
       <c r="AB128" s="23"/>
       <c r="AC128" s="23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AD128" s="23"/>
       <c r="AE128" s="23"/>
@@ -29928,10 +29930,10 @@
         <v>Winter warm spell</v>
       </c>
       <c r="E129" s="51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F129" s="51" t="s">
         <v>1035</v>
-      </c>
-      <c r="F129" s="51" t="s">
-        <v>1036</v>
       </c>
       <c r="G129" s="46" t="s">
         <v>34</v>
@@ -29955,10 +29957,10 @@
       </c>
       <c r="O129" s="48"/>
       <c r="P129" s="56" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q129" s="56" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R129" s="48" t="s">
         <v>62</v>
@@ -29986,7 +29988,7 @@
       <c r="AA129" s="43"/>
       <c r="AB129" s="23"/>
       <c r="AC129" s="23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AD129" s="23"/>
       <c r="AE129" s="23"/>
@@ -30010,10 +30012,10 @@
         <v>Winter warm spell</v>
       </c>
       <c r="E130" s="51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F130" s="51" t="s">
         <v>1035</v>
-      </c>
-      <c r="F130" s="51" t="s">
-        <v>1036</v>
       </c>
       <c r="G130" s="46" t="s">
         <v>34</v>
@@ -30037,10 +30039,10 @@
       </c>
       <c r="O130" s="48"/>
       <c r="P130" s="56" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="Q130" s="56" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R130" s="48" t="s">
         <v>62</v>
@@ -30068,7 +30070,7 @@
       <c r="AA130" s="43"/>
       <c r="AB130" s="23"/>
       <c r="AC130" s="23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AD130" s="23"/>
       <c r="AE130" s="23"/>
@@ -30092,10 +30094,10 @@
         <v>Winter warm spell</v>
       </c>
       <c r="E131" s="51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F131" s="51" t="s">
         <v>1035</v>
-      </c>
-      <c r="F131" s="51" t="s">
-        <v>1036</v>
       </c>
       <c r="G131" s="46" t="s">
         <v>34</v>
@@ -30112,7 +30114,7 @@
         <v>102</v>
       </c>
       <c r="M131" s="76" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="N131" s="43" t="s">
         <v>533</v>
@@ -30122,7 +30124,7 @@
         <v>534</v>
       </c>
       <c r="Q131" s="56" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R131" s="43" t="s">
         <v>62</v>
@@ -30150,7 +30152,7 @@
       <c r="AA131" s="43"/>
       <c r="AB131" s="23"/>
       <c r="AC131" s="23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AD131" s="23"/>
       <c r="AE131" s="23"/>
@@ -30173,10 +30175,10 @@
         <v>522</v>
       </c>
       <c r="E132" s="51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F132" s="51" t="s">
         <v>1035</v>
-      </c>
-      <c r="F132" s="51" t="s">
-        <v>1036</v>
       </c>
       <c r="G132" s="89" t="s">
         <v>34</v>
@@ -30193,17 +30195,17 @@
         <v>102</v>
       </c>
       <c r="M132" s="76" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N132" s="43" t="s">
         <v>1043</v>
-      </c>
-      <c r="N132" s="43" t="s">
-        <v>1044</v>
       </c>
       <c r="O132" s="48"/>
       <c r="P132" s="56" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q132" s="48" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R132" s="48" t="s">
         <v>175</v>
@@ -30231,7 +30233,7 @@
       <c r="AA132" s="90"/>
       <c r="AB132" s="90"/>
       <c r="AC132" s="23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AD132" s="90"/>
       <c r="AE132" s="90"/>
@@ -30251,13 +30253,13 @@
         <v>37</v>
       </c>
       <c r="D133" s="99" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E133" s="19" t="s">
         <v>1046</v>
       </c>
-      <c r="E133" s="19" t="s">
-        <v>1047</v>
-      </c>
       <c r="F133" s="19" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G133" s="48"/>
       <c r="H133" s="89"/>
@@ -30265,7 +30267,7 @@
         <v>37</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>37</v>
@@ -30274,14 +30276,14 @@
         <v>37</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="N133" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O133" s="7"/>
       <c r="P133" s="7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q133" s="7" t="s">
         <v>37</v>
@@ -30338,13 +30340,13 @@
         <v>37</v>
       </c>
       <c r="D134" s="99" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E134" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="E134" s="7" t="s">
-        <v>1050</v>
-      </c>
       <c r="F134" s="7" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G134" s="48"/>
       <c r="H134" s="89"/>
@@ -30352,7 +30354,7 @@
         <v>37</v>
       </c>
       <c r="J134" s="6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="K134" s="6" t="s">
         <v>37</v>
@@ -30361,14 +30363,14 @@
         <v>37</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="N134" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O134" s="7"/>
       <c r="P134" s="7" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q134" s="7" t="s">
         <v>37</v>
@@ -30392,7 +30394,7 @@
         <v>37</v>
       </c>
       <c r="X134" s="120" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="Y134" s="125"/>
       <c r="Z134" s="7" t="s">
@@ -30427,13 +30429,13 @@
         <v>37</v>
       </c>
       <c r="D135" s="99" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E135" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="E135" s="6" t="s">
-        <v>1054</v>
-      </c>
       <c r="F135" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G135" s="48"/>
       <c r="H135" s="89"/>
@@ -30441,7 +30443,7 @@
         <v>37</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="K135" s="6" t="s">
         <v>37</v>
@@ -30450,14 +30452,14 @@
         <v>37</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N135" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O135" s="7"/>
       <c r="P135" s="7" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q135" s="7" t="s">
         <v>37</v>
@@ -30514,7 +30516,7 @@
         <v>37</v>
       </c>
       <c r="D136" s="99" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E136" s="142"/>
       <c r="G136" s="48"/>
@@ -30532,14 +30534,14 @@
         <v>37</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N136" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O136" s="7"/>
       <c r="P136" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="Q136" s="7" t="s">
         <v>37</v>
@@ -30682,37 +30684,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="31" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1059</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="C1" s="30" t="s">
         <v>1060</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>1061</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>1062</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>1063</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>1064</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>1065</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>1066</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>1067</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="30" t="s">
         <v>1068</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="12" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -30720,34 +30722,34 @@
         <v>166</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>166</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>1071</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="28" t="s">
         <v>1073</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="H2" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -30755,14 +30757,14 @@
         <v>496</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11" t="s">
         <v>496</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>226</v>
@@ -30771,16 +30773,16 @@
         <v>32</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -30788,28 +30790,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E4" s="29" t="s">
         <v>1083</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>1084</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -30817,10 +30819,10 @@
         <v>273</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>1089</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>1090</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="29" t="s">
@@ -30830,7 +30832,7 @@
         <v>70</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>166</v>
@@ -30839,10 +30841,10 @@
         <v>302</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>1092</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -30850,14 +30852,14 @@
         <v>112</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
         <v>133</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>82</v>
@@ -30866,7 +30868,7 @@
         <v>99</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>301</v>
@@ -30875,17 +30877,17 @@
         <v>112</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="12" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="11" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>245</v>
@@ -30894,19 +30896,19 @@
         <v>112</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -30914,28 +30916,28 @@
         <v>264</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E8" s="29" t="s">
         <v>1105</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>1106</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>167</v>
       </c>
       <c r="G8" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -30943,30 +30945,30 @@
         <v>56</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G9" s="28" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>1113</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>1114</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
         <v>496</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -30974,10 +30976,10 @@
         <v>303</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E10" s="29" t="s">
         <v>1116</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>1117</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>188</v>
@@ -30991,7 +30993,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -30999,24 +31001,24 @@
         <v>100</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>322</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>226</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -31030,17 +31032,17 @@
         <v>335</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G12" t="s">
         <v>1123</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="I12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -31048,44 +31050,44 @@
         <v>303</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E13" s="29" t="s">
         <v>1127</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="F13" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>1129</v>
-      </c>
       <c r="G13" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>496</v>
       </c>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E14" s="29" t="s">
         <v>1131</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="F14" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" t="s">
         <v>1133</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -31093,26 +31095,26 @@
         <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="29" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" t="s">
         <v>1139</v>
       </c>
-      <c r="G15" t="s">
-        <v>1140</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -31120,26 +31122,26 @@
         <v>264</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="29" t="s">
         <v>1143</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="F16" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>1145</v>
-      </c>
       <c r="G16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>322</v>
       </c>
       <c r="I16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -31147,20 +31149,20 @@
         <v>384</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>322</v>
       </c>
       <c r="G17" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="I17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -31168,7 +31170,7 @@
         <v>324</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>496</v>
@@ -31180,7 +31182,7 @@
         <v>300</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="I18" s="1"/>
       <c r="K18" s="1" t="s">
@@ -31192,25 +31194,25 @@
         <v>342</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G19" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E20" s="29"/>
       <c r="F20" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G20" t="s">
         <v>1153</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1154</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>140</v>
@@ -31222,10 +31224,10 @@
         <v>310</v>
       </c>
       <c r="G21" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -31234,7 +31236,7 @@
         <v>420</v>
       </c>
       <c r="G22" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>496</v>
@@ -31249,7 +31251,7 @@
         <v>273</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -31257,10 +31259,10 @@
         <v>245</v>
       </c>
       <c r="G24" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -31268,7 +31270,7 @@
         <v>36</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -31281,10 +31283,10 @@
     </row>
     <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="F27" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>1160</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -31292,7 +31294,7 @@
         <v>343</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -31300,18 +31302,18 @@
         <v>498</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F30" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F31" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -31340,19 +31342,19 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1169</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1170</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>21</v>
@@ -31364,10 +31366,10 @@
         <v>18</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>1171</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>1172</v>
       </c>
       <c r="K1" s="3"/>
       <c r="O1" s="3"/>
@@ -31377,7 +31379,7 @@
         <v>324</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C2" t="s">
         <v>102</v>
@@ -31398,7 +31400,7 @@
         <v>86</v>
       </c>
       <c r="J2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -31406,7 +31408,7 @@
         <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C3" t="s">
         <v>125</v>
@@ -31427,7 +31429,7 @@
         <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -31435,7 +31437,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
@@ -31456,7 +31458,7 @@
         <v>216</v>
       </c>
       <c r="J4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -31464,7 +31466,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C5" t="s">
         <v>198</v>
@@ -31479,7 +31481,7 @@
         <v>129</v>
       </c>
       <c r="I5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -31499,7 +31501,7 @@
         <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="135" x14ac:dyDescent="0.25">
@@ -31510,13 +31512,13 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" t="s">
         <v>1179</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -31533,7 +31535,7 @@
         <v>222</v>
       </c>
       <c r="I8" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -31544,7 +31546,7 @@
         <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H9" t="s">
         <v>510</v>
@@ -31561,10 +31563,10 @@
         <v>378</v>
       </c>
       <c r="H10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I10" t="s">
         <v>1183</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -31575,7 +31577,7 @@
         <v>465</v>
       </c>
       <c r="I11" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
@@ -31602,7 +31604,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I14" t="s">
         <v>470</v>
@@ -31610,27 +31612,27 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
@@ -31650,7 +31652,7 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="30" x14ac:dyDescent="0.25">
@@ -31685,7 +31687,7 @@
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="30" x14ac:dyDescent="0.25">
@@ -31700,12 +31702,12 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
@@ -31755,6 +31757,124 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2265d2cf-dc49-4f73-81a7-3266a36d53af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="61170afc-8edf-4b61-a019-dc093f4e4a16" xsi:nil="true"/>
+    <SharedWithUsers xmlns="61170afc-8edf-4b61-a019-dc093f4e4a16">
+      <UserInfo>
+        <DisplayName>Murdock,Trevor (he, him, they, them | il, iel, iel) (ECCC)</DisplayName>
+        <AccountId>47</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lizee,Teah (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>30</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fyke,Jeremy (il | he, him) (ECCC)</DisplayName>
+        <AccountId>25</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Pomeroy,Carrington (ECCC)</DisplayName>
+        <AccountId>20</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Barrow,Elaine (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>18</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rayfield,Sarah (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Bilodeau,Etienne (il | he, him) (ECCC)</DisplayName>
+        <AccountId>57</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lagace,Amanda (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>124</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Churchill,Callie (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>287</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Campagne,Philippine (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>350</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jafarpur,Pouriya (ECCC)</DisplayName>
+        <AccountId>97</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Smith,Ryan (il | he, him) (ECCC)</DisplayName>
+        <AccountId>42</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Clunas,Casey (ECCC)</DisplayName>
+        <AccountId>38</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Nakoneczny,Sonya (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>217</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Pond,Ellen (ECCC)</DisplayName>
+        <AccountId>222</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Madge,Carly (ECCC)</DisplayName>
+        <AccountId>430</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Krause,Sonya (ECCC)</DisplayName>
+        <AccountId>84</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kumar,Erin (elle | she, her) (ECCC)</DisplayName>
+        <AccountId>434</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Morris,Michael (il | he, him) (ECCC)</DisplayName>
+        <AccountId>480</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <Comments xmlns="2265d2cf-dc49-4f73-81a7-3266a36d53af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E6B34C521C601B4F9DCE921A7DEE7460" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6a32d9ba70d69eed7a686568ac3c5820">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2265d2cf-dc49-4f73-81a7-3266a36d53af" xmlns:ns3="61170afc-8edf-4b61-a019-dc093f4e4a16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e8cdc6d8172c9863b1701d1f996f3fc" ns2:_="" ns3:_="">
     <xsd:import namespace="2265d2cf-dc49-4f73-81a7-3266a36d53af"/>
@@ -32011,139 +32131,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2265d2cf-dc49-4f73-81a7-3266a36d53af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="61170afc-8edf-4b61-a019-dc093f4e4a16" xsi:nil="true"/>
-    <SharedWithUsers xmlns="61170afc-8edf-4b61-a019-dc093f4e4a16">
-      <UserInfo>
-        <DisplayName>Murdock,Trevor (he, him, they, them | il, iel, iel) (ECCC)</DisplayName>
-        <AccountId>47</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lizee,Teah (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>30</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fyke,Jeremy (il | he, him) (ECCC)</DisplayName>
-        <AccountId>25</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Pomeroy,Carrington (ECCC)</DisplayName>
-        <AccountId>20</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Barrow,Elaine (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>18</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rayfield,Sarah (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Bilodeau,Etienne (il | he, him) (ECCC)</DisplayName>
-        <AccountId>57</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lagace,Amanda (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>124</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Churchill,Callie (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>287</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Campagne,Philippine (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>350</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jafarpur,Pouriya (ECCC)</DisplayName>
-        <AccountId>97</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Smith,Ryan (il | he, him) (ECCC)</DisplayName>
-        <AccountId>42</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Clunas,Casey (ECCC)</DisplayName>
-        <AccountId>38</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Nakoneczny,Sonya (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>217</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Pond,Ellen (ECCC)</DisplayName>
-        <AccountId>222</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Madge,Carly (ECCC)</DisplayName>
-        <AccountId>430</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Krause,Sonya (ECCC)</DisplayName>
-        <AccountId>84</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kumar,Erin (elle | she, her) (ECCC)</DisplayName>
-        <AccountId>434</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Morris,Michael (il | he, him) (ECCC)</DisplayName>
-        <AccountId>480</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <Comments xmlns="2265d2cf-dc49-4f73-81a7-3266a36d53af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26C29487-5C6F-442D-8E5D-60D5DE6C1D92}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EB05AA6-EDE6-4019-B1FE-3731D1DA4B24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2265d2cf-dc49-4f73-81a7-3266a36d53af"/>
-    <ds:schemaRef ds:uri="61170afc-8edf-4b61-a019-dc093f4e4a16"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32166,9 +32157,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EB05AA6-EDE6-4019-B1FE-3731D1DA4B24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26C29487-5C6F-442D-8E5D-60D5DE6C1D92}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2265d2cf-dc49-4f73-81a7-3266a36d53af"/>
+    <ds:schemaRef ds:uri="61170afc-8edf-4b61-a019-dc093f4e4a16"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>